--- a/out/S03_employee_training_feedback/agent3/agent3_test_cases_with_paths.xlsx
+++ b/out/S03_employee_training_feedback/agent3/agent3_test_cases_with_paths.xlsx
@@ -906,7 +906,7 @@
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
-          <t>12 test(s): TC-FT23, TC-FT24, TC-FT25, TC-FT26, TC-FT27, TC-FT28 ...</t>
+          <t>10 test(s): TC-FT20, TC-FT21, TC-FT22, TC-FT23, TC-FT24, TC-FT25 ...</t>
         </is>
       </c>
       <c r="Q7" s="8" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
-          <t>27 test(s): TC-FT05, TC-FT06, TC-FT07, TC-FT08, TC-FT09, TC-FT10 ...</t>
+          <t>24 test(s): TC-FT05, TC-FT06, TC-FT07, TC-FT08, TC-FT09, TC-FT10 ...</t>
         </is>
       </c>
       <c r="Q8" s="8" t="inlineStr">
@@ -1027,7 +1027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE49"/>
+  <dimension ref="A1:AE44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>DT1</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>3. Dependency / Piping</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -2370,27 +2370,27 @@
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>DT1 quotes the answer given at S1</t>
+          <t>Q1 accepts a normal answer and the survey moves on</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>Prove DT1's wording is built from the answer given at S1, so the respondent is only asked about what they actually chose.</t>
+          <t>Prove that answering Q1 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>A question that quotes the wrong earlier answer reads as a different question entirely to the respondent.</t>
+          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
         </is>
       </c>
       <c r="K12" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L12" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q5=No) as far as DT1.</t>
+          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q1.</t>
         </is>
       </c>
       <c r="M12" s="6" t="inlineStr">
@@ -2400,8 +2400,8 @@
       </c>
       <c r="N12" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes
-then: After submitting S2, look for DT1 on the next page. Do not answer it.</t>
+          <t>S1 = Yes; S2 = Yes; Q1 = In person; Q2 = Very poor; Q3 = Very poor; Q4 = Content relevance; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
+then: Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="O12" s="6" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
-          <t>Every answer before DT1 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at DT1 is the one the claim turns on.</t>
+          <t>Every answer before Q1 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q1 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q12" s="6" t="inlineStr">
         <is>
-          <t>After submitting S2, look for DT1 on the next page. Do not answer it.</t>
+          <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="R12" s="6" t="inlineStr">
@@ -2446,7 +2446,8 @@
       </c>
       <c r="W12" s="6" t="inlineStr">
         <is>
-          <t>1. DT1's wording includes: Yes</t>
+          <t>1. Q1 is on screen
+2. the next question shown is Q2</t>
         </is>
       </c>
       <c r="X12" s="6" t="inlineStr">
@@ -2461,7 +2462,7 @@
       </c>
       <c r="Z12" s="6" t="inlineStr">
         <is>
-          <t>DT1 | Great, you're eligible for this survey! Next, a few quick questions about your recent training session. | text display | — | Always show</t>
+          <t>Q1 | Which channel did you primarily use for this training session? | single | In person; Live virtual; Self-paced online | Always show</t>
         </is>
       </c>
       <c r="AA12" s="6" t="inlineStr">
@@ -2481,7 +2482,7 @@
       </c>
       <c r="AD12" s="6" t="inlineStr">
         <is>
-          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE12" s="6" t="inlineStr">
@@ -2511,12 +2512,12 @@
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10. Negative / Robustness</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
@@ -2526,22 +2527,22 @@
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>Q1 accepts a normal answer and the survey moves on</t>
+          <t>Q1 blocks a blank answer</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>Prove that answering Q1 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
+          <t>Prove Q1 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L13" s="6" t="inlineStr">
@@ -2556,13 +2557,13 @@
       </c>
       <c r="N13" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; Q1 = In person; Q2 = Very poor; Q3 = Very poor; Q4 = Content relevance; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
-then: Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>S1 = Yes; S2 = Yes
+then: At Q1, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="O13" s="6" t="inlineStr">
         <is>
-          <t>VALID_TYPICAL for every answer</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="P13" s="6" t="inlineStr">
@@ -2572,17 +2573,17 @@
       </c>
       <c r="Q13" s="6" t="inlineStr">
         <is>
-          <t>Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>At Q1, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="R13" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1  (refused at Q1; respondent stays put)</t>
         </is>
       </c>
       <c r="S13" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
+          <t>S1, S2, DT1, Q1</t>
         </is>
       </c>
       <c r="T13" s="6" t="inlineStr">
@@ -2592,23 +2593,23 @@
       </c>
       <c r="U13" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
         </is>
       </c>
       <c r="V13" s="6" t="inlineStr">
         <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
+          <t>No forward navigation - the same question must reappear.</t>
         </is>
       </c>
       <c r="W13" s="6" t="inlineStr">
         <is>
-          <t>1. Q1 is on screen
-2. the next question shown is Q2</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q1</t>
         </is>
       </c>
       <c r="X13" s="6" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>Not reached - the respondent cannot progress</t>
         </is>
       </c>
       <c r="Y13" s="6" t="inlineStr">
@@ -2638,7 +2639,7 @@
       </c>
       <c r="AD13" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
         </is>
       </c>
       <c r="AE13" s="6" t="inlineStr">
@@ -2653,7 +2654,7 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -2668,12 +2669,12 @@
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>2. Input Validation</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>10. Negative / Robustness</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G14" s="7" t="inlineStr">
@@ -2683,27 +2684,27 @@
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>Q1 blocks a blank answer</t>
+          <t>Q2 accepts a normal answer and the survey moves on</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>Prove Q1 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
+          <t>Prove that answering Q2 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
         </is>
       </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L14" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q1.</t>
+          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q2.</t>
         </is>
       </c>
       <c r="M14" s="6" t="inlineStr">
@@ -2713,33 +2714,33 @@
       </c>
       <c r="N14" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes
-then: At Q1, select nothing at all, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; Q1 = In person; Q2 = Very poor; Q3 = Very poor; Q4 = Content relevance; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
+then: Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="O14" s="6" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q1 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q1 is the one the claim turns on.</t>
+          <t>Every answer before Q2 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q2 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q14" s="6" t="inlineStr">
         <is>
-          <t>At Q1, select nothing at all, then submit.</t>
+          <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="R14" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1  (refused at Q1; respondent stays put)</t>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
         </is>
       </c>
       <c r="S14" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, DT1, Q1</t>
+          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
         </is>
       </c>
       <c r="T14" s="6" t="inlineStr">
@@ -2749,23 +2750,23 @@
       </c>
       <c r="U14" s="6" t="inlineStr">
         <is>
-          <t>Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
+          <t>none</t>
         </is>
       </c>
       <c r="V14" s="6" t="inlineStr">
         <is>
-          <t>No forward navigation - the same question must reappear.</t>
+          <t>Each listed question is followed immediately by the next in the sequence.</t>
         </is>
       </c>
       <c r="W14" s="6" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q1</t>
+          <t>1. Q2 is on screen
+2. the next question shown is Q3</t>
         </is>
       </c>
       <c r="X14" s="6" t="inlineStr">
         <is>
-          <t>Not reached - the respondent cannot progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="Y14" s="6" t="inlineStr">
@@ -2775,7 +2776,7 @@
       </c>
       <c r="Z14" s="6" t="inlineStr">
         <is>
-          <t>Q1 | Which channel did you primarily use for this training session? | single | In person; Live virtual; Self-paced online | Always show</t>
+          <t>Q2 | Overall, how satisfied were you with the training session? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Always show</t>
         </is>
       </c>
       <c r="AA14" s="6" t="inlineStr">
@@ -2795,7 +2796,7 @@
       </c>
       <c r="AD14" s="6" t="inlineStr">
         <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE14" s="6" t="inlineStr">
@@ -2810,7 +2811,7 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -2825,12 +2826,12 @@
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>3. Dependency / Piping</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10. Negative / Robustness</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
@@ -2840,17 +2841,17 @@
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>Q1 quotes the answer given at S1</t>
+          <t>Q2 blocks a blank answer</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>Prove Q1's wording is built from the answer given at S1, so the respondent is only asked about what they actually chose.</t>
+          <t>Prove Q2 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>A question that quotes the wrong earlier answer reads as a different question entirely to the respondent.</t>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
@@ -2860,7 +2861,7 @@
       </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q1.</t>
+          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q2.</t>
         </is>
       </c>
       <c r="M15" s="6" t="inlineStr">
@@ -2870,33 +2871,33 @@
       </c>
       <c r="N15" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes
-then: At Q1, choose “In person”, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; Q1 = In person
+then: At Q2, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="O15" s="6" t="inlineStr">
         <is>
-          <t>VALID_TYPICAL for every answer</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q1 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q1 is the one the claim turns on.</t>
+          <t>Every answer before Q2 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q2 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q15" s="6" t="inlineStr">
         <is>
-          <t>At Q1, choose “In person”, then submit.</t>
+          <t>At Q2, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="R15" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2  (refused at Q2; respondent stays put)</t>
         </is>
       </c>
       <c r="S15" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
+          <t>S1, S2, DT1, Q1, Q2</t>
         </is>
       </c>
       <c r="T15" s="6" t="inlineStr">
@@ -2906,22 +2907,23 @@
       </c>
       <c r="U15" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>Q3, Q4, Q5, Q6, Q7, Q8</t>
         </is>
       </c>
       <c r="V15" s="6" t="inlineStr">
         <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
+          <t>No forward navigation - the same question must reappear.</t>
         </is>
       </c>
       <c r="W15" s="6" t="inlineStr">
         <is>
-          <t>1. Q1's wording includes: Yes</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q2</t>
         </is>
       </c>
       <c r="X15" s="6" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>Not reached - the respondent cannot progress</t>
         </is>
       </c>
       <c r="Y15" s="6" t="inlineStr">
@@ -2931,7 +2933,7 @@
       </c>
       <c r="Z15" s="6" t="inlineStr">
         <is>
-          <t>Q1 | Which channel did you primarily use for this training session? | single | In person; Live virtual; Self-paced online | Always show</t>
+          <t>Q2 | Overall, how satisfied were you with the training session? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Always show</t>
         </is>
       </c>
       <c r="AA15" s="6" t="inlineStr">
@@ -2951,7 +2953,7 @@
       </c>
       <c r="AD15" s="6" t="inlineStr">
         <is>
-          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
         </is>
       </c>
       <c r="AE15" s="6" t="inlineStr">
@@ -2966,7 +2968,7 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -2996,12 +2998,12 @@
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>Q2 accepts a normal answer and the survey moves on</t>
+          <t>Q3 accepts a normal answer and the survey moves on</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>Prove that answering Q2 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
+          <t>Prove that answering Q3 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
         </is>
       </c>
       <c r="J16" s="6" t="inlineStr">
@@ -3016,7 +3018,7 @@
       </c>
       <c r="L16" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q2.</t>
+          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q3.</t>
         </is>
       </c>
       <c r="M16" s="6" t="inlineStr">
@@ -3037,7 +3039,7 @@
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q2 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q2 is the one the claim turns on.</t>
+          <t>Every answer before Q3 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q3 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q16" s="6" t="inlineStr">
@@ -3072,8 +3074,8 @@
       </c>
       <c r="W16" s="6" t="inlineStr">
         <is>
-          <t>1. Q2 is on screen
-2. the next question shown is Q3</t>
+          <t>1. Q3 is on screen
+2. the next question shown is Q4_SQ001</t>
         </is>
       </c>
       <c r="X16" s="6" t="inlineStr">
@@ -3088,7 +3090,7 @@
       </c>
       <c r="Z16" s="6" t="inlineStr">
         <is>
-          <t>Q2 | Overall, how satisfied were you with the training session? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Always show</t>
+          <t>Q3 | How easy was it to complete what you wanted to do? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Always show</t>
         </is>
       </c>
       <c r="AA16" s="6" t="inlineStr">
@@ -3123,7 +3125,7 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -3153,12 +3155,12 @@
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>Q2 blocks a blank answer</t>
+          <t>Q3 blocks a blank answer</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>Prove Q2 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
+          <t>Prove Q3 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
         </is>
       </c>
       <c r="J17" s="6" t="inlineStr">
@@ -3173,7 +3175,7 @@
       </c>
       <c r="L17" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q2.</t>
+          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q3.</t>
         </is>
       </c>
       <c r="M17" s="6" t="inlineStr">
@@ -3183,8 +3185,8 @@
       </c>
       <c r="N17" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; Q1 = In person
-then: At Q2, select nothing at all, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; Q1 = In person; Q2 = Very poor
+then: At Q3, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="O17" s="6" t="inlineStr">
@@ -3194,22 +3196,22 @@
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q2 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q2 is the one the claim turns on.</t>
+          <t>Every answer before Q3 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q3 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q17" s="6" t="inlineStr">
         <is>
-          <t>At Q2, select nothing at all, then submit.</t>
+          <t>At Q3, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="R17" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2  (refused at Q2; respondent stays put)</t>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3  (refused at Q3; respondent stays put)</t>
         </is>
       </c>
       <c r="S17" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, DT1, Q1, Q2</t>
+          <t>S1, S2, DT1, Q1, Q2, Q3</t>
         </is>
       </c>
       <c r="T17" s="6" t="inlineStr">
@@ -3219,7 +3221,7 @@
       </c>
       <c r="U17" s="6" t="inlineStr">
         <is>
-          <t>Q3, Q4, Q5, Q6, Q7, Q8</t>
+          <t>Q4, Q5, Q6, Q7, Q8</t>
         </is>
       </c>
       <c r="V17" s="6" t="inlineStr">
@@ -3230,7 +3232,7 @@
       <c r="W17" s="6" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q2</t>
+2. an error message is shown against Q3</t>
         </is>
       </c>
       <c r="X17" s="6" t="inlineStr">
@@ -3245,7 +3247,7 @@
       </c>
       <c r="Z17" s="6" t="inlineStr">
         <is>
-          <t>Q2 | Overall, how satisfied were you with the training session? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Always show</t>
+          <t>Q3 | How easy was it to complete what you wanted to do? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Always show</t>
         </is>
       </c>
       <c r="AA17" s="6" t="inlineStr">
@@ -3280,7 +3282,7 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -3295,7 +3297,7 @@
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>3. Dependency / Piping</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -3310,27 +3312,27 @@
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>Q2 quotes the answer given at S1</t>
+          <t>Q4 accepts a normal answer and the survey moves on</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
-          <t>Prove Q2's wording is built from the answer given at S1, so the respondent is only asked about what they actually chose.</t>
+          <t>Prove that answering Q4 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
         </is>
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>A question that quotes the wrong earlier answer reads as a different question entirely to the respondent.</t>
+          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
         </is>
       </c>
       <c r="K18" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L18" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q2.</t>
+          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q4.</t>
         </is>
       </c>
       <c r="M18" s="6" t="inlineStr">
@@ -3340,8 +3342,8 @@
       </c>
       <c r="N18" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; Q1 = In person
-then: At Q2, choose “Very poor”, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; Q1 = In person; Q2 = Very poor; Q3 = Very poor; Q4 = Content relevance; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
+then: Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="O18" s="6" t="inlineStr">
@@ -3351,12 +3353,12 @@
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q2 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q2 is the one the claim turns on.</t>
+          <t>Every answer before Q4 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q4 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q18" s="6" t="inlineStr">
         <is>
-          <t>At Q2, choose “Very poor”, then submit.</t>
+          <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="R18" s="6" t="inlineStr">
@@ -3386,7 +3388,8 @@
       </c>
       <c r="W18" s="6" t="inlineStr">
         <is>
-          <t>1. Q2's wording includes: Yes</t>
+          <t>1. Q4 is on screen
+2. the next question shown is Q5</t>
         </is>
       </c>
       <c r="X18" s="6" t="inlineStr">
@@ -3401,7 +3404,7 @@
       </c>
       <c r="Z18" s="6" t="inlineStr">
         <is>
-          <t>Q2 | Overall, how satisfied were you with the training session? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Always show</t>
+          <t>Q4 | Which aspects influenced your rating? Select all that apply. | multi | Content relevance; Instructor quality; Exercises; Pace; Materials; Technology | Validate: {"min_selections": 1}</t>
         </is>
       </c>
       <c r="AA18" s="6" t="inlineStr">
@@ -3421,7 +3424,7 @@
       </c>
       <c r="AD18" s="6" t="inlineStr">
         <is>
-          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE18" s="6" t="inlineStr">
@@ -3436,7 +3439,7 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -3451,7 +3454,7 @@
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
@@ -3466,17 +3469,17 @@
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>Q3 accepts a normal answer and the survey moves on</t>
+          <t>Q4 accepts a valid answer</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>Prove that answering Q3 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
+          <t>Prove Q4 accepts an answer that obeys its stated rule. The rule is: at least 1 option must be selected</t>
         </is>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
+          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
@@ -3486,7 +3489,7 @@
       </c>
       <c r="L19" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q3.</t>
+          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q4.</t>
         </is>
       </c>
       <c r="M19" s="6" t="inlineStr">
@@ -3496,23 +3499,23 @@
       </c>
       <c r="N19" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; Q1 = In person; Q2 = Very poor; Q3 = Very poor; Q4 = Content relevance; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
-then: Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>S1 = Yes; S2 = Yes; Q1 = In person; Q2 = Very poor; Q3 = Very poor
+then: At Q4, tick 1 option (Content relevance), then submit.</t>
         </is>
       </c>
       <c r="O19" s="6" t="inlineStr">
         <is>
-          <t>VALID_TYPICAL for every answer</t>
+          <t>VALID_BOUNDARY</t>
         </is>
       </c>
       <c r="P19" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q3 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q3 is the one the claim turns on.</t>
+          <t>Every answer before Q4 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q4 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q19" s="6" t="inlineStr">
         <is>
-          <t>Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>At Q4, tick 1 option (Content relevance), then submit.</t>
         </is>
       </c>
       <c r="R19" s="6" t="inlineStr">
@@ -3542,8 +3545,7 @@
       </c>
       <c r="W19" s="6" t="inlineStr">
         <is>
-          <t>1. Q3 is on screen
-2. the next question shown is Q4_SQ001</t>
+          <t>1. the survey ACCEPTS the answer and moves on</t>
         </is>
       </c>
       <c r="X19" s="6" t="inlineStr">
@@ -3558,7 +3560,7 @@
       </c>
       <c r="Z19" s="6" t="inlineStr">
         <is>
-          <t>Q3 | How easy was it to complete what you wanted to do? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Always show</t>
+          <t>Q4 | Which aspects influenced your rating? Select all that apply. | multi | Content relevance; Instructor quality; Exercises; Pace; Materials; Technology | Validate: {"min_selections": 1}</t>
         </is>
       </c>
       <c r="AA19" s="6" t="inlineStr">
@@ -3578,7 +3580,7 @@
       </c>
       <c r="AD19" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE19" s="6" t="inlineStr">
@@ -3593,7 +3595,7 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -3623,27 +3625,27 @@
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>Q3 blocks a blank answer</t>
+          <t>Q4 rejects an invalid answer</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t>Prove Q3 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
+          <t>Prove Q4 refuses an answer that breaks its stated rule. The rule is: at least 1 option must be selected</t>
         </is>
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
         </is>
       </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L20" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q3.</t>
+          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q4.</t>
         </is>
       </c>
       <c r="M20" s="6" t="inlineStr">
@@ -3653,33 +3655,33 @@
       </c>
       <c r="N20" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; Q1 = In person; Q2 = Very poor
-then: At Q3, select nothing at all, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; Q1 = In person; Q2 = Very poor; Q3 = Very poor
+then: At Q4, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="O20" s="6" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>INVALID_BOUNDARY</t>
         </is>
       </c>
       <c r="P20" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q3 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q3 is the one the claim turns on.</t>
+          <t>Every answer before Q4 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q4 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q20" s="6" t="inlineStr">
         <is>
-          <t>At Q3, select nothing at all, then submit.</t>
+          <t>At Q4, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="R20" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3  (refused at Q3; respondent stays put)</t>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4  (refused at Q4; respondent stays put)</t>
         </is>
       </c>
       <c r="S20" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, DT1, Q1, Q2, Q3</t>
+          <t>S1, S2, DT1, Q1, Q2, Q3, Q4</t>
         </is>
       </c>
       <c r="T20" s="6" t="inlineStr">
@@ -3689,7 +3691,7 @@
       </c>
       <c r="U20" s="6" t="inlineStr">
         <is>
-          <t>Q4, Q5, Q6, Q7, Q8</t>
+          <t>Q5, Q6, Q7, Q8</t>
         </is>
       </c>
       <c r="V20" s="6" t="inlineStr">
@@ -3700,7 +3702,7 @@
       <c r="W20" s="6" t="inlineStr">
         <is>
           <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q3</t>
+2. an error message is shown against Q4</t>
         </is>
       </c>
       <c r="X20" s="6" t="inlineStr">
@@ -3715,7 +3717,7 @@
       </c>
       <c r="Z20" s="6" t="inlineStr">
         <is>
-          <t>Q3 | How easy was it to complete what you wanted to do? | single | 1 - Very poor; 2 - Poor; 3 - Fair; 4 - Good; 5 - Excellent | Always show</t>
+          <t>Q4 | Which aspects influenced your rating? Select all that apply. | multi | Content relevance; Instructor quality; Exercises; Pace; Materials; Technology | Validate: {"min_selections": 1}</t>
         </is>
       </c>
       <c r="AA20" s="6" t="inlineStr">
@@ -3735,7 +3737,7 @@
       </c>
       <c r="AD20" s="6" t="inlineStr">
         <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE20" s="6" t="inlineStr">
@@ -3765,12 +3767,12 @@
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10. Negative / Robustness</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
@@ -3780,22 +3782,22 @@
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>Q4 accepts a normal answer and the survey moves on</t>
+          <t>Q4 blocks a blank answer</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>Prove that answering Q4 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
+          <t>Prove Q4 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a multi question.</t>
         </is>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L21" s="6" t="inlineStr">
@@ -3810,13 +3812,13 @@
       </c>
       <c r="N21" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; Q1 = In person; Q2 = Very poor; Q3 = Very poor; Q4 = Content relevance; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
-then: Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>S1 = Yes; S2 = Yes; Q1 = In person; Q2 = Very poor; Q3 = Very poor
+then: At Q4, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="O21" s="6" t="inlineStr">
         <is>
-          <t>VALID_TYPICAL for every answer</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="P21" s="6" t="inlineStr">
@@ -3826,17 +3828,17 @@
       </c>
       <c r="Q21" s="6" t="inlineStr">
         <is>
-          <t>Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>At Q4, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="R21" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4  (refused at Q4; respondent stays put)</t>
         </is>
       </c>
       <c r="S21" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
+          <t>S1, S2, DT1, Q1, Q2, Q3, Q4</t>
         </is>
       </c>
       <c r="T21" s="6" t="inlineStr">
@@ -3846,23 +3848,23 @@
       </c>
       <c r="U21" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>Q5, Q6, Q7, Q8</t>
         </is>
       </c>
       <c r="V21" s="6" t="inlineStr">
         <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
+          <t>No forward navigation - the same question must reappear.</t>
         </is>
       </c>
       <c r="W21" s="6" t="inlineStr">
         <is>
-          <t>1. Q4 is on screen
-2. the next question shown is Q5</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q4</t>
         </is>
       </c>
       <c r="X21" s="6" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>Not reached - the respondent cannot progress</t>
         </is>
       </c>
       <c r="Y21" s="6" t="inlineStr">
@@ -3892,7 +3894,7 @@
       </c>
       <c r="AD21" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
         </is>
       </c>
       <c r="AE21" s="6" t="inlineStr">
@@ -3907,7 +3909,7 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -3922,7 +3924,7 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>2. Input Validation</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -3937,17 +3939,17 @@
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>Q4 accepts a valid answer</t>
+          <t>Q5 accepts a normal answer and the survey moves on</t>
         </is>
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
-          <t>Prove Q4 accepts an answer that obeys its stated rule. The rule is: at least 1 option must be selected</t>
+          <t>Prove that answering Q5 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
         </is>
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
-          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
+          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
         </is>
       </c>
       <c r="K22" s="6" t="inlineStr">
@@ -3957,7 +3959,7 @@
       </c>
       <c r="L22" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q4.</t>
+          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q5.</t>
         </is>
       </c>
       <c r="M22" s="6" t="inlineStr">
@@ -3967,23 +3969,23 @@
       </c>
       <c r="N22" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; Q1 = In person; Q2 = Very poor; Q3 = Very poor
-then: At Q4, tick 1 option (Content relevance), then submit.</t>
+          <t>S1 = Yes; S2 = Yes; Q1 = In person; Q2 = Very poor; Q3 = Very poor; Q4 = Content relevance; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
+then: Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="O22" s="6" t="inlineStr">
         <is>
-          <t>VALID_BOUNDARY</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P22" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q4 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q4 is the one the claim turns on.</t>
+          <t>Every answer before Q5 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q5 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q22" s="6" t="inlineStr">
         <is>
-          <t>At Q4, tick 1 option (Content relevance), then submit.</t>
+          <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="R22" s="6" t="inlineStr">
@@ -4013,7 +4015,8 @@
       </c>
       <c r="W22" s="6" t="inlineStr">
         <is>
-          <t>1. the survey ACCEPTS the answer and moves on</t>
+          <t>1. Q5 is on screen
+2. the next question shown is Q6</t>
         </is>
       </c>
       <c r="X22" s="6" t="inlineStr">
@@ -4028,7 +4031,7 @@
       </c>
       <c r="Z22" s="6" t="inlineStr">
         <is>
-          <t>Q4 | Which aspects influenced your rating? Select all that apply. | multi | Content relevance; Instructor quality; Exercises; Pace; Materials; Technology | Validate: {"min_selections": 1}</t>
+          <t>Q5 | Did you encounter a problem? | single | Yes; No | Always show</t>
         </is>
       </c>
       <c r="AA22" s="6" t="inlineStr">
@@ -4048,7 +4051,7 @@
       </c>
       <c r="AD22" s="6" t="inlineStr">
         <is>
-          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE22" s="6" t="inlineStr">
@@ -4063,7 +4066,7 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -4078,12 +4081,12 @@
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>2. Input Validation</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>10. Negative / Robustness</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
@@ -4093,17 +4096,17 @@
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>Q4 rejects an invalid answer</t>
+          <t>R4 jumps forward when its condition is met</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>Prove Q4 refuses an answer that breaks its stated rule. The rule is: at least 1 option must be selected</t>
+          <t>Prove R4 jumps to Q7. The rule is: Q5 == 'No'</t>
         </is>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
+          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
@@ -4113,7 +4116,7 @@
       </c>
       <c r="L23" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q4.</t>
+          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q5.</t>
         </is>
       </c>
       <c r="M23" s="6" t="inlineStr">
@@ -4123,33 +4126,33 @@
       </c>
       <c r="N23" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; Q1 = In person; Q2 = Very poor; Q3 = Very poor
-then: At Q4, select nothing at all, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; Q1 = In person; Q2 = Very poor; Q3 = Very poor; Q4 = Content relevance
+then: At Q5, choose “No”, then submit.</t>
         </is>
       </c>
       <c r="O23" s="6" t="inlineStr">
         <is>
-          <t>INVALID_BOUNDARY</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P23" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q4 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q4 is the one the claim turns on.</t>
+          <t>Every answer before Q5 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q5 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q23" s="6" t="inlineStr">
         <is>
-          <t>At Q4, select nothing at all, then submit.</t>
+          <t>At Q5, choose “No”, then submit.</t>
         </is>
       </c>
       <c r="R23" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4  (refused at Q4; respondent stays put)</t>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q7 -&gt; Q8</t>
         </is>
       </c>
       <c r="S23" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, DT1, Q1, Q2, Q3, Q4</t>
+          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q7, Q8</t>
         </is>
       </c>
       <c r="T23" s="6" t="inlineStr">
@@ -4159,23 +4162,22 @@
       </c>
       <c r="U23" s="6" t="inlineStr">
         <is>
-          <t>Q5, Q6, Q7, Q8</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="V23" s="6" t="inlineStr">
         <is>
-          <t>No forward navigation - the same question must reappear.</t>
+          <t>Each listed question is followed immediately by the next in the sequence.</t>
         </is>
       </c>
       <c r="W23" s="6" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q4</t>
+          <t>1. the next question shown is Q7</t>
         </is>
       </c>
       <c r="X23" s="6" t="inlineStr">
         <is>
-          <t>Not reached - the respondent cannot progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="Y23" s="6" t="inlineStr">
@@ -4185,7 +4187,8 @@
       </c>
       <c r="Z23" s="6" t="inlineStr">
         <is>
-          <t>Q4 | Which aspects influenced your rating? Select all that apply. | multi | Content relevance; Instructor quality; Exercises; Pace; Materials; Technology | Validate: {"min_selections": 1}</t>
+          <t>Q5 | Did you encounter a problem? | single | Yes; No | Always show
+Rules exercised: R4</t>
         </is>
       </c>
       <c r="AA23" s="6" t="inlineStr">
@@ -4193,9 +4196,9 @@
           <t>QRE explicit - stated directly in the questionnaire.</t>
         </is>
       </c>
-      <c r="AB23" s="8" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
+      <c r="AB23" s="10" t="inlineStr">
+        <is>
+          <t>PROVISIONAL</t>
         </is>
       </c>
       <c r="AC23" s="8" t="inlineStr">
@@ -4205,12 +4208,12 @@
       </c>
       <c r="AD23" s="6" t="inlineStr">
         <is>
-          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE23" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Leans on an unconfirmed reading: rule_precedence</t>
         </is>
       </c>
     </row>
@@ -4220,7 +4223,7 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -4235,7 +4238,7 @@
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>2. Input Validation</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
@@ -4250,27 +4253,27 @@
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>Q4 blocks a blank answer</t>
+          <t>R4 does not jump when its condition is not met</t>
         </is>
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
-          <t>Prove Q4 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a multi question.</t>
+          <t>Prove R4 does not jump and the respondent continues in sequence. The rule is: Q5 == 'No'</t>
         </is>
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
         </is>
       </c>
       <c r="K24" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L24" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q4.</t>
+          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q5.</t>
         </is>
       </c>
       <c r="M24" s="6" t="inlineStr">
@@ -4280,33 +4283,33 @@
       </c>
       <c r="N24" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; Q1 = In person; Q2 = Very poor; Q3 = Very poor
-then: At Q4, select nothing at all, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; Q1 = In person; Q2 = Very poor; Q3 = Very poor; Q4 = Content relevance
+then: At Q5, choose “Yes”, then submit.</t>
         </is>
       </c>
       <c r="O24" s="6" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P24" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q4 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q4 is the one the claim turns on.</t>
+          <t>Every answer before Q5 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q5 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q24" s="6" t="inlineStr">
         <is>
-          <t>At Q4, select nothing at all, then submit.</t>
+          <t>At Q5, choose “Yes”, then submit.</t>
         </is>
       </c>
       <c r="R24" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4  (refused at Q4; respondent stays put)</t>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
         </is>
       </c>
       <c r="S24" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, DT1, Q1, Q2, Q3, Q4</t>
+          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
         </is>
       </c>
       <c r="T24" s="6" t="inlineStr">
@@ -4316,23 +4319,22 @@
       </c>
       <c r="U24" s="6" t="inlineStr">
         <is>
-          <t>Q5, Q6, Q7, Q8</t>
+          <t>none</t>
         </is>
       </c>
       <c r="V24" s="6" t="inlineStr">
         <is>
-          <t>No forward navigation - the same question must reappear.</t>
+          <t>Each listed question is followed immediately by the next in the sequence.</t>
         </is>
       </c>
       <c r="W24" s="6" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q4</t>
+          <t>1. the next question shown is Q6</t>
         </is>
       </c>
       <c r="X24" s="6" t="inlineStr">
         <is>
-          <t>Not reached - the respondent cannot progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="Y24" s="6" t="inlineStr">
@@ -4342,7 +4344,8 @@
       </c>
       <c r="Z24" s="6" t="inlineStr">
         <is>
-          <t>Q4 | Which aspects influenced your rating? Select all that apply. | multi | Content relevance; Instructor quality; Exercises; Pace; Materials; Technology | Validate: {"min_selections": 1}</t>
+          <t>Q5 | Did you encounter a problem? | single | Yes; No | Always show
+Rules exercised: R4</t>
         </is>
       </c>
       <c r="AA24" s="6" t="inlineStr">
@@ -4362,7 +4365,7 @@
       </c>
       <c r="AD24" s="6" t="inlineStr">
         <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE24" s="6" t="inlineStr">
@@ -4392,12 +4395,12 @@
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10. Negative / Robustness</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
@@ -4407,22 +4410,22 @@
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>Q5 accepts a normal answer and the survey moves on</t>
+          <t>Q5 blocks a blank answer</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>Prove that answering Q5 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
+          <t>Prove Q5 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
         </is>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
         </is>
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L25" s="6" t="inlineStr">
@@ -4437,13 +4440,13 @@
       </c>
       <c r="N25" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; Q1 = In person; Q2 = Very poor; Q3 = Very poor; Q4 = Content relevance; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
-then: Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>S1 = Yes; S2 = Yes; Q1 = In person; Q2 = Very poor; Q3 = Very poor; Q4 = Content relevance
+then: At Q5, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="O25" s="6" t="inlineStr">
         <is>
-          <t>VALID_TYPICAL for every answer</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="P25" s="6" t="inlineStr">
@@ -4453,17 +4456,17 @@
       </c>
       <c r="Q25" s="6" t="inlineStr">
         <is>
-          <t>Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>At Q5, select nothing at all, then submit.</t>
         </is>
       </c>
       <c r="R25" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5  (refused at Q5; respondent stays put)</t>
         </is>
       </c>
       <c r="S25" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
+          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5</t>
         </is>
       </c>
       <c r="T25" s="6" t="inlineStr">
@@ -4473,23 +4476,23 @@
       </c>
       <c r="U25" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>Q6, Q7, Q8</t>
         </is>
       </c>
       <c r="V25" s="6" t="inlineStr">
         <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
+          <t>No forward navigation - the same question must reappear.</t>
         </is>
       </c>
       <c r="W25" s="6" t="inlineStr">
         <is>
-          <t>1. Q5 is on screen
-2. the next question shown is Q6</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q5</t>
         </is>
       </c>
       <c r="X25" s="6" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>Not reached - the respondent cannot progress</t>
         </is>
       </c>
       <c r="Y25" s="6" t="inlineStr">
@@ -4519,7 +4522,7 @@
       </c>
       <c r="AD25" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
         </is>
       </c>
       <c r="AE25" s="6" t="inlineStr">
@@ -4534,7 +4537,7 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Q5</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -4559,17 +4562,17 @@
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P03</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>R4 jumps forward when its condition is met</t>
+          <t>Q6 accepts a normal answer and the survey moves on</t>
         </is>
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>Prove R4 jumps to Q7. The rule is: Q5 == 'No'</t>
+          <t>Prove that answering Q6 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
         </is>
       </c>
       <c r="J26" s="6" t="inlineStr">
@@ -4584,7 +4587,7 @@
       </c>
       <c r="L26" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q5.</t>
+          <t>Travel path P03 (Completing respondent — Q5=Yes) as far as Q6.</t>
         </is>
       </c>
       <c r="M26" s="6" t="inlineStr">
@@ -4594,8 +4597,8 @@
       </c>
       <c r="N26" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; Q1 = In person; Q2 = Very poor; Q3 = Very poor; Q4 = Content relevance
-then: At Q5, choose “No”, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; Q1 = In person; Q2 = Very poor; Q3 = Very poor; Q4 = Content relevance; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
+then: Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="O26" s="6" t="inlineStr">
@@ -4605,32 +4608,32 @@
       </c>
       <c r="P26" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q5 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q5 is the one the claim turns on.</t>
+          <t>Every answer before Q6 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q6 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q26" s="6" t="inlineStr">
         <is>
-          <t>At Q5, choose “No”, then submit.</t>
+          <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
       <c r="R26" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q7 -&gt; Q8</t>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
         </is>
       </c>
       <c r="S26" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q7, Q8</t>
+          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
         </is>
       </c>
       <c r="T26" s="6" t="inlineStr">
         <is>
-          <t>Q6</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U26" s="6" t="inlineStr">
         <is>
-          <t>Q6</t>
+          <t>none</t>
         </is>
       </c>
       <c r="V26" s="6" t="inlineStr">
@@ -4640,7 +4643,8 @@
       </c>
       <c r="W26" s="6" t="inlineStr">
         <is>
-          <t>1. the next question shown is Q7</t>
+          <t>1. Q6 is on screen
+2. the next question shown is Q7</t>
         </is>
       </c>
       <c r="X26" s="6" t="inlineStr">
@@ -4655,18 +4659,18 @@
       </c>
       <c r="Z26" s="6" t="inlineStr">
         <is>
-          <t>Q5 | Did you encounter a problem? | single | Yes; No | Always show
-Rules exercised: R4</t>
+          <t>Q6 | Please describe the main problem. | text | — | Show if: Q5 == 'Yes'
+Validate: {"min_length": 10, "max_length": 500}</t>
         </is>
       </c>
       <c r="AA26" s="6" t="inlineStr">
         <is>
-          <t>QRE explicit - stated directly in the questionnaire.</t>
-        </is>
-      </c>
-      <c r="AB26" s="10" t="inlineStr">
-        <is>
-          <t>PROVISIONAL</t>
+          <t>Derived by rule from the questionnaire's own tables.</t>
+        </is>
+      </c>
+      <c r="AB26" s="8" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
         </is>
       </c>
       <c r="AC26" s="8" t="inlineStr">
@@ -4676,12 +4680,12 @@
       </c>
       <c r="AD26" s="6" t="inlineStr">
         <is>
-          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE26" s="6" t="inlineStr">
         <is>
-          <t>Leans on an unconfirmed reading: rule_precedence</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4695,7 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Q5</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
@@ -4711,22 +4715,22 @@
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>10. Negative / Robustness</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P03</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>R4 does not jump when its condition is not met</t>
+          <t>Q6 is shown when its condition is met</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>Prove R4 does not jump and the respondent continues in sequence. The rule is: Q5 == 'No'</t>
+          <t>Prove Q6 IS shown when its display rule is satisfied. The rule is: Q5 == 'Yes'</t>
         </is>
       </c>
       <c r="J27" s="6" t="inlineStr">
@@ -4741,7 +4745,7 @@
       </c>
       <c r="L27" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q5.</t>
+          <t>Travel path P03 (Completing respondent — Q5=Yes) as far as Q6.</t>
         </is>
       </c>
       <c r="M27" s="6" t="inlineStr">
@@ -4751,8 +4755,8 @@
       </c>
       <c r="N27" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; Q1 = In person; Q2 = Very poor; Q3 = Very poor; Q4 = Content relevance
-then: At Q5, choose “Yes”, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; Q1 = In person; Q2 = Very poor; Q3 = Very poor; Q4 = Content relevance; Q5 = Yes
+then: At Q6, type “xxxxxxxxxx”, then submit.</t>
         </is>
       </c>
       <c r="O27" s="6" t="inlineStr">
@@ -4762,12 +4766,12 @@
       </c>
       <c r="P27" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q5 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q5 is the one the claim turns on.</t>
+          <t>Every answer before Q6 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q6 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q27" s="6" t="inlineStr">
         <is>
-          <t>At Q5, choose “Yes”, then submit.</t>
+          <t>At Q6, type “xxxxxxxxxx”, then submit.</t>
         </is>
       </c>
       <c r="R27" s="6" t="inlineStr">
@@ -4782,7 +4786,7 @@
       </c>
       <c r="T27" s="6" t="inlineStr">
         <is>
-          <t>Q6</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U27" s="6" t="inlineStr">
@@ -4797,7 +4801,7 @@
       </c>
       <c r="W27" s="6" t="inlineStr">
         <is>
-          <t>1. the next question shown is Q6</t>
+          <t>1. Q6 is on screen</t>
         </is>
       </c>
       <c r="X27" s="6" t="inlineStr">
@@ -4812,13 +4816,14 @@
       </c>
       <c r="Z27" s="6" t="inlineStr">
         <is>
-          <t>Q5 | Did you encounter a problem? | single | Yes; No | Always show
-Rules exercised: R4</t>
+          <t>Q6 | Please describe the main problem. | text | — | Show if: Q5 == 'Yes'
+Validate: {"min_length": 10, "max_length": 500}
+Rules exercised: R3</t>
         </is>
       </c>
       <c r="AA27" s="6" t="inlineStr">
         <is>
-          <t>QRE explicit - stated directly in the questionnaire.</t>
+          <t>Derived by rule from the questionnaire's own tables.</t>
         </is>
       </c>
       <c r="AB27" s="8" t="inlineStr">
@@ -4848,7 +4853,7 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>Q5</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
@@ -4863,7 +4868,7 @@
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>2. Input Validation</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
@@ -4873,32 +4878,32 @@
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P03</t>
         </is>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>Q5 blocks a blank answer</t>
+          <t>Q6 is not shown when its condition is not met</t>
         </is>
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
-          <t>Prove Q5 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
+          <t>Prove Q6 is NOT shown when its display rule is not satisfied. The rule is: Q5 == 'Yes'</t>
         </is>
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
         </is>
       </c>
       <c r="K28" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L28" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q5.</t>
+          <t>Travel path P03 (Completing respondent — Q5=Yes) as far as Q6.</t>
         </is>
       </c>
       <c r="M28" s="6" t="inlineStr">
@@ -4908,59 +4913,59 @@
       </c>
       <c r="N28" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; Q1 = In person; Q2 = Very poor; Q3 = Very poor; Q4 = Content relevance
-then: At Q5, select nothing at all, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; Q1 = In person; Q2 = Very poor; Q3 = Very poor; Q4 = Content relevance; Q5 = No
+then: After submitting Q5, look for Q6 on the next page. Do not answer it.</t>
         </is>
       </c>
       <c r="O28" s="6" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>VALID_TYPICAL (the branch that hides the question)</t>
         </is>
       </c>
       <c r="P28" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q5 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q5 is the one the claim turns on.</t>
+          <t>Every answer before Q6 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q6 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q28" s="6" t="inlineStr">
         <is>
-          <t>At Q5, select nothing at all, then submit.</t>
+          <t>After submitting Q5, look for Q6 on the next page. Do not answer it.</t>
         </is>
       </c>
       <c r="R28" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5  (refused at Q5; respondent stays put)</t>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q7 -&gt; Q8</t>
         </is>
       </c>
       <c r="S28" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5</t>
+          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q7, Q8</t>
         </is>
       </c>
       <c r="T28" s="6" t="inlineStr">
         <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="U28" s="6" t="inlineStr">
+        <is>
           <t>Q6</t>
         </is>
       </c>
-      <c r="U28" s="6" t="inlineStr">
-        <is>
-          <t>Q6, Q7, Q8</t>
-        </is>
-      </c>
       <c r="V28" s="6" t="inlineStr">
         <is>
-          <t>No forward navigation - the same question must reappear.</t>
+          <t>Each listed question is followed immediately by the next in the sequence.</t>
         </is>
       </c>
       <c r="W28" s="6" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q5</t>
+          <t>1. Q6 is NOT on screen
+2. the respondent carries on rather than being screened out or finished</t>
         </is>
       </c>
       <c r="X28" s="6" t="inlineStr">
         <is>
-          <t>Not reached - the respondent cannot progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="Y28" s="6" t="inlineStr">
@@ -4970,17 +4975,19 @@
       </c>
       <c r="Z28" s="6" t="inlineStr">
         <is>
-          <t>Q5 | Did you encounter a problem? | single | Yes; No | Always show</t>
+          <t>Q6 | Please describe the main problem. | text | — | Show if: Q5 == 'Yes'
+Validate: {"min_length": 10, "max_length": 500}
+Rules exercised: R3</t>
         </is>
       </c>
       <c r="AA28" s="6" t="inlineStr">
         <is>
-          <t>QRE explicit - stated directly in the questionnaire.</t>
-        </is>
-      </c>
-      <c r="AB28" s="8" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
+          <t>Derived by rule from the questionnaire's own tables.</t>
+        </is>
+      </c>
+      <c r="AB28" s="10" t="inlineStr">
+        <is>
+          <t>PROVISIONAL</t>
         </is>
       </c>
       <c r="AC28" s="8" t="inlineStr">
@@ -4990,12 +4997,12 @@
       </c>
       <c r="AD28" s="6" t="inlineStr">
         <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+          <t>It does not prove why the question was absent beyond the display rule; the check confirms the respondent was still travelling and had not been screened out. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE28" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Leans on an unconfirmed reading: rule_precedence</t>
         </is>
       </c>
     </row>
@@ -5020,7 +5027,7 @@
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
@@ -5035,17 +5042,17 @@
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>Q6 accepts a normal answer and the survey moves on</t>
+          <t>Q6 accepts a valid answer</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>Prove that answering Q6 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
+          <t>Prove Q6 accepts an answer that obeys its stated rule. The rule is: at least 10 characters; at most 500 characters</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
+          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
         </is>
       </c>
       <c r="K29" s="6" t="inlineStr">
@@ -5065,13 +5072,13 @@
       </c>
       <c r="N29" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; Q1 = In person; Q2 = Very poor; Q3 = Very poor; Q4 = Content relevance; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
-then: Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>S1 = Yes; S2 = Yes; Q1 = In person; Q2 = Very poor; Q3 = Very poor; Q4 = Content relevance; Q5 = Yes
+then: At Q6, type “xxxxxxxxxx”, then submit.</t>
         </is>
       </c>
       <c r="O29" s="6" t="inlineStr">
         <is>
-          <t>VALID_TYPICAL for every answer</t>
+          <t>VALID_BOUNDARY</t>
         </is>
       </c>
       <c r="P29" s="6" t="inlineStr">
@@ -5081,7 +5088,7 @@
       </c>
       <c r="Q29" s="6" t="inlineStr">
         <is>
-          <t>Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>At Q6, type “xxxxxxxxxx”, then submit.</t>
         </is>
       </c>
       <c r="R29" s="6" t="inlineStr">
@@ -5111,8 +5118,7 @@
       </c>
       <c r="W29" s="6" t="inlineStr">
         <is>
-          <t>1. Q6 is on screen
-2. the next question shown is Q7</t>
+          <t>1. the survey ACCEPTS the answer and moves on</t>
         </is>
       </c>
       <c r="X29" s="6" t="inlineStr">
@@ -5148,7 +5154,7 @@
       </c>
       <c r="AD29" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE29" s="6" t="inlineStr">
@@ -5178,12 +5184,12 @@
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10. Negative / Robustness</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
@@ -5193,17 +5199,17 @@
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>Q6 is shown when its condition is met</t>
+          <t>Q6 rejects an invalid answer</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>Prove Q6 IS shown when its display rule is satisfied. The rule is: Q5 == 'Yes'</t>
+          <t>Prove Q6 refuses an answer that breaks its stated rule. The rule is: at least 10 characters; at most 500 characters</t>
         </is>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
+          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
         </is>
       </c>
       <c r="K30" s="6" t="inlineStr">
@@ -5224,12 +5230,12 @@
       <c r="N30" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; Q1 = In person; Q2 = Very poor; Q3 = Very poor; Q4 = Content relevance; Q5 = Yes
-then: At Q6, type “xxxxxxxxxx”, then submit.</t>
+then: At Q6, type a 501-character answer, then submit.</t>
         </is>
       </c>
       <c r="O30" s="6" t="inlineStr">
         <is>
-          <t>VALID_TYPICAL for every answer</t>
+          <t>INVALID_BOUNDARY</t>
         </is>
       </c>
       <c r="P30" s="6" t="inlineStr">
@@ -5239,17 +5245,17 @@
       </c>
       <c r="Q30" s="6" t="inlineStr">
         <is>
-          <t>At Q6, type “xxxxxxxxxx”, then submit.</t>
+          <t>At Q6, type a 501-character answer, then submit.</t>
         </is>
       </c>
       <c r="R30" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6  (refused at Q6; respondent stays put)</t>
         </is>
       </c>
       <c r="S30" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
+          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6</t>
         </is>
       </c>
       <c r="T30" s="6" t="inlineStr">
@@ -5259,22 +5265,23 @@
       </c>
       <c r="U30" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>Q7, Q8</t>
         </is>
       </c>
       <c r="V30" s="6" t="inlineStr">
         <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
+          <t>No forward navigation - the same question must reappear.</t>
         </is>
       </c>
       <c r="W30" s="6" t="inlineStr">
         <is>
-          <t>1. Q6 is on screen</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q6</t>
         </is>
       </c>
       <c r="X30" s="6" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>Not reached - the respondent cannot progress</t>
         </is>
       </c>
       <c r="Y30" s="6" t="inlineStr">
@@ -5285,8 +5292,7 @@
       <c r="Z30" s="6" t="inlineStr">
         <is>
           <t>Q6 | Please describe the main problem. | text | — | Show if: Q5 == 'Yes'
-Validate: {"min_length": 10, "max_length": 500}
-Rules exercised: R3</t>
+Validate: {"min_length": 10, "max_length": 500}</t>
         </is>
       </c>
       <c r="AA30" s="6" t="inlineStr">
@@ -5306,7 +5312,7 @@
       </c>
       <c r="AD30" s="6" t="inlineStr">
         <is>
-          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE30" s="6" t="inlineStr">
@@ -5336,7 +5342,7 @@
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
@@ -5351,22 +5357,22 @@
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>Q6 is not shown when its condition is not met</t>
+          <t>Q6 blocks a blank answer</t>
         </is>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>Prove Q6 is NOT shown when its display rule is not satisfied. The rule is: Q5 == 'Yes'</t>
+          <t>Prove Q6 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a text question.</t>
         </is>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
         </is>
       </c>
       <c r="K31" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L31" s="6" t="inlineStr">
@@ -5381,13 +5387,13 @@
       </c>
       <c r="N31" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; Q1 = In person; Q2 = Very poor; Q3 = Very poor; Q4 = Content relevance; Q5 = No
-then: After submitting Q5, look for Q6 on the next page. Do not answer it.</t>
+          <t>S1 = Yes; S2 = Yes; Q1 = In person; Q2 = Very poor; Q3 = Very poor; Q4 = Content relevance; Q5 = Yes
+then: At Q6, type nothing, then submit.</t>
         </is>
       </c>
       <c r="O31" s="6" t="inlineStr">
         <is>
-          <t>VALID_TYPICAL (the branch that hides the question)</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="P31" s="6" t="inlineStr">
@@ -5397,17 +5403,17 @@
       </c>
       <c r="Q31" s="6" t="inlineStr">
         <is>
-          <t>After submitting Q5, look for Q6 on the next page. Do not answer it.</t>
+          <t>At Q6, type nothing, then submit.</t>
         </is>
       </c>
       <c r="R31" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q7 -&gt; Q8</t>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6  (refused at Q6; respondent stays put)</t>
         </is>
       </c>
       <c r="S31" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q7, Q8</t>
+          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6</t>
         </is>
       </c>
       <c r="T31" s="6" t="inlineStr">
@@ -5417,23 +5423,23 @@
       </c>
       <c r="U31" s="6" t="inlineStr">
         <is>
-          <t>Q6</t>
+          <t>Q7, Q8</t>
         </is>
       </c>
       <c r="V31" s="6" t="inlineStr">
         <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
+          <t>No forward navigation - the same question must reappear.</t>
         </is>
       </c>
       <c r="W31" s="6" t="inlineStr">
         <is>
-          <t>1. Q6 is NOT on screen
-2. the respondent carries on rather than being screened out or finished</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q6</t>
         </is>
       </c>
       <c r="X31" s="6" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>Not reached - the respondent cannot progress</t>
         </is>
       </c>
       <c r="Y31" s="6" t="inlineStr">
@@ -5444,8 +5450,7 @@
       <c r="Z31" s="6" t="inlineStr">
         <is>
           <t>Q6 | Please describe the main problem. | text | — | Show if: Q5 == 'Yes'
-Validate: {"min_length": 10, "max_length": 500}
-Rules exercised: R3</t>
+Validate: {"min_length": 10, "max_length": 500}</t>
         </is>
       </c>
       <c r="AA31" s="6" t="inlineStr">
@@ -5453,9 +5458,9 @@
           <t>Derived by rule from the questionnaire's own tables.</t>
         </is>
       </c>
-      <c r="AB31" s="10" t="inlineStr">
-        <is>
-          <t>PROVISIONAL</t>
+      <c r="AB31" s="8" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
         </is>
       </c>
       <c r="AC31" s="8" t="inlineStr">
@@ -5465,12 +5470,12 @@
       </c>
       <c r="AD31" s="6" t="inlineStr">
         <is>
-          <t>It does not prove why the question was absent beyond the display rule; the check confirms the respondent was still travelling and had not been screened out. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
         </is>
       </c>
       <c r="AE31" s="6" t="inlineStr">
         <is>
-          <t>Leans on an unconfirmed reading: rule_precedence</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5510,12 +5515,12 @@
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>Q6 accepts a valid answer</t>
+          <t>Q6 rejects an invalid answer</t>
         </is>
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
-          <t>Prove Q6 accepts an answer that obeys its stated rule. The rule is: at least 10 characters; at most 500 characters</t>
+          <t>Prove Q6 refuses an answer that breaks its stated rule. The rule is: at least 10 characters; at most 500 characters</t>
         </is>
       </c>
       <c r="J32" s="6" t="inlineStr">
@@ -5541,12 +5546,12 @@
       <c r="N32" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; Q1 = In person; Q2 = Very poor; Q3 = Very poor; Q4 = Content relevance; Q5 = Yes
-then: At Q6, type “xxxxxxxxxx”, then submit.</t>
+then: At Q6, type a 500-character answer, then submit.</t>
         </is>
       </c>
       <c r="O32" s="6" t="inlineStr">
         <is>
-          <t>VALID_BOUNDARY</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P32" s="6" t="inlineStr">
@@ -5556,7 +5561,7 @@
       </c>
       <c r="Q32" s="6" t="inlineStr">
         <is>
-          <t>At Q6, type “xxxxxxxxxx”, then submit.</t>
+          <t>At Q6, type a 500-character answer, then submit.</t>
         </is>
       </c>
       <c r="R32" s="6" t="inlineStr">
@@ -5657,7 +5662,7 @@
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>10. Negative / Robustness</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
@@ -5698,12 +5703,12 @@
       <c r="N33" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; Q1 = In person; Q2 = Very poor; Q3 = Very poor; Q4 = Content relevance; Q5 = Yes
-then: At Q6, type a 501-character answer, then submit.</t>
+then: At Q6, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
         </is>
       </c>
       <c r="O33" s="6" t="inlineStr">
         <is>
-          <t>INVALID_BOUNDARY</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P33" s="6" t="inlineStr">
@@ -5713,17 +5718,17 @@
       </c>
       <c r="Q33" s="6" t="inlineStr">
         <is>
-          <t>At Q6, type a 501-character answer, then submit.</t>
+          <t>At Q6, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
         </is>
       </c>
       <c r="R33" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6  (refused at Q6; respondent stays put)</t>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
         </is>
       </c>
       <c r="S33" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6</t>
+          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
         </is>
       </c>
       <c r="T33" s="6" t="inlineStr">
@@ -5733,23 +5738,22 @@
       </c>
       <c r="U33" s="6" t="inlineStr">
         <is>
-          <t>Q7, Q8</t>
+          <t>none</t>
         </is>
       </c>
       <c r="V33" s="6" t="inlineStr">
         <is>
-          <t>No forward navigation - the same question must reappear.</t>
+          <t>Each listed question is followed immediately by the next in the sequence.</t>
         </is>
       </c>
       <c r="W33" s="6" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q6</t>
+          <t>1. the survey ACCEPTS the answer and moves on</t>
         </is>
       </c>
       <c r="X33" s="6" t="inlineStr">
         <is>
-          <t>Not reached - the respondent cannot progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="Y33" s="6" t="inlineStr">
@@ -5815,7 +5819,7 @@
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>10. Negative / Robustness</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
@@ -5825,12 +5829,12 @@
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>Q6 blocks a blank answer</t>
+          <t>Q6 allows a blank answer, being optional</t>
         </is>
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>Prove Q6 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a text question.</t>
+          <t>Prove Q6 lets the respondent through with no answer, because the questionnaire marks it optional.</t>
         </is>
       </c>
       <c r="J34" s="6" t="inlineStr">
@@ -5856,12 +5860,12 @@
       <c r="N34" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; Q1 = In person; Q2 = Very poor; Q3 = Very poor; Q4 = Content relevance; Q5 = Yes
-then: At Q6, type nothing, then submit.</t>
+then: At Q6, type 3 spaces and nothing else, then submit.</t>
         </is>
       </c>
       <c r="O34" s="6" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P34" s="6" t="inlineStr">
@@ -5871,7 +5875,7 @@
       </c>
       <c r="Q34" s="6" t="inlineStr">
         <is>
-          <t>At Q6, type nothing, then submit.</t>
+          <t>At Q6, type 3 spaces and nothing else, then submit.</t>
         </is>
       </c>
       <c r="R34" s="6" t="inlineStr">
@@ -5926,9 +5930,9 @@
           <t>Derived by rule from the questionnaire's own tables.</t>
         </is>
       </c>
-      <c r="AB34" s="8" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
+      <c r="AB34" s="10" t="inlineStr">
+        <is>
+          <t>PROVISIONAL</t>
         </is>
       </c>
       <c r="AC34" s="8" t="inlineStr">
@@ -5943,7 +5947,7 @@
       </c>
       <c r="AE34" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Leans on an unconfirmed reading: whitespace_is_an_answer</t>
         </is>
       </c>
     </row>
@@ -5953,105 +5957,105 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
+          <t>Q7</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>TC-FT29</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>FOCUSED</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>1. Flow / Routing</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>Q7 accepts a normal answer and the survey moves on</t>
+        </is>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>Prove that answering Q7 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
+        </is>
+      </c>
+      <c r="K35" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L35" s="6" t="inlineStr">
+        <is>
+          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q7.</t>
+        </is>
+      </c>
+      <c r="M35" s="6" t="inlineStr">
+        <is>
+          <t>FRESH_RESPONDENT</t>
+        </is>
+      </c>
+      <c r="N35" s="6" t="inlineStr">
+        <is>
+          <t>S1 = Yes; S2 = Yes; Q1 = In person; Q2 = Very poor; Q3 = Very poor; Q4 = Content relevance; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
+then: Answer through the whole survey as listed, then observe where it ends.</t>
+        </is>
+      </c>
+      <c r="O35" s="6" t="inlineStr">
+        <is>
+          <t>VALID_TYPICAL for every answer</t>
+        </is>
+      </c>
+      <c r="P35" s="6" t="inlineStr">
+        <is>
+          <t>Every answer before Q7 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q7 is the one the claim turns on.</t>
+        </is>
+      </c>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>Answer through the whole survey as listed, then observe where it ends.</t>
+        </is>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
+        </is>
+      </c>
+      <c r="S35" s="6" t="inlineStr">
+        <is>
+          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
+        </is>
+      </c>
+      <c r="T35" s="6" t="inlineStr">
+        <is>
           <t>Q6</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
-        <is>
-          <t>TC-FT29</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>FOCUSED</t>
-        </is>
-      </c>
-      <c r="E35" s="6" t="inlineStr">
-        <is>
-          <t>3. Dependency / Piping</t>
-        </is>
-      </c>
-      <c r="F35" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G35" s="7" t="inlineStr">
-        <is>
-          <t>P03</t>
-        </is>
-      </c>
-      <c r="H35" s="6" t="inlineStr">
-        <is>
-          <t>Q6 quotes the answer given at Q5</t>
-        </is>
-      </c>
-      <c r="I35" s="6" t="inlineStr">
-        <is>
-          <t>Prove Q6's wording is built from the answer given at Q5, so the respondent is only asked about what they actually chose.</t>
-        </is>
-      </c>
-      <c r="J35" s="6" t="inlineStr">
-        <is>
-          <t>A question that quotes the wrong earlier answer reads as a different question entirely to the respondent.</t>
-        </is>
-      </c>
-      <c r="K35" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="L35" s="6" t="inlineStr">
-        <is>
-          <t>Travel path P03 (Completing respondent — Q5=Yes) as far as Q6.</t>
-        </is>
-      </c>
-      <c r="M35" s="6" t="inlineStr">
-        <is>
-          <t>FRESH_RESPONDENT</t>
-        </is>
-      </c>
-      <c r="N35" s="6" t="inlineStr">
-        <is>
-          <t>S1 = Yes; S2 = Yes; Q1 = In person; Q2 = Very poor; Q3 = Very poor; Q4 = Content relevance; Q5 = Yes
-then: At Q6, type “xxxxxxxxxx”, then submit.</t>
-        </is>
-      </c>
-      <c r="O35" s="6" t="inlineStr">
-        <is>
-          <t>VALID_TYPICAL for every answer</t>
-        </is>
-      </c>
-      <c r="P35" s="6" t="inlineStr">
-        <is>
-          <t>Every answer before Q6 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q6 is the one the claim turns on.</t>
-        </is>
-      </c>
-      <c r="Q35" s="6" t="inlineStr">
-        <is>
-          <t>At Q6, type “xxxxxxxxxx”, then submit.</t>
-        </is>
-      </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
-        </is>
-      </c>
-      <c r="S35" s="6" t="inlineStr">
-        <is>
-          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
-        </is>
-      </c>
-      <c r="T35" s="6" t="inlineStr">
+      <c r="U35" s="6" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="U35" s="6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
       <c r="V35" s="6" t="inlineStr">
         <is>
           <t>Each listed question is followed immediately by the next in the sequence.</t>
@@ -6059,7 +6063,8 @@
       </c>
       <c r="W35" s="6" t="inlineStr">
         <is>
-          <t>1. Q6's wording includes: Yes</t>
+          <t>1. Q7 is on screen
+2. the next question shown is Q8</t>
         </is>
       </c>
       <c r="X35" s="6" t="inlineStr">
@@ -6074,8 +6079,7 @@
       </c>
       <c r="Z35" s="6" t="inlineStr">
         <is>
-          <t>Q6 | Please describe the main problem. | text | — | Show if: Q5 == 'Yes'
-Validate: {"min_length": 10, "max_length": 500}</t>
+          <t>Q7 | How likely are you to recommend this service? | single | 0; 1; 2; 3; 4; 5; 6; 7; 8; 9; 10 | Always show</t>
         </is>
       </c>
       <c r="AA35" s="6" t="inlineStr">
@@ -6095,7 +6099,7 @@
       </c>
       <c r="AD35" s="6" t="inlineStr">
         <is>
-          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE35" s="6" t="inlineStr">
@@ -6110,119 +6114,119 @@
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
+          <t>Q7</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>TC-FT30</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>FOCUSED</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>2. Input Validation</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>10. Negative / Robustness</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>Q7 blocks a blank answer</t>
+        </is>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>Prove Q7 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+        </is>
+      </c>
+      <c r="K36" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L36" s="6" t="inlineStr">
+        <is>
+          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q7.</t>
+        </is>
+      </c>
+      <c r="M36" s="6" t="inlineStr">
+        <is>
+          <t>FRESH_RESPONDENT</t>
+        </is>
+      </c>
+      <c r="N36" s="6" t="inlineStr">
+        <is>
+          <t>S1 = Yes; S2 = Yes; Q1 = In person; Q2 = Very poor; Q3 = Very poor; Q4 = Content relevance; Q5 = Yes; Q6 = xxxxxxxxxx
+then: At Q7, select nothing at all, then submit.</t>
+        </is>
+      </c>
+      <c r="O36" s="6" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="P36" s="6" t="inlineStr">
+        <is>
+          <t>Every answer before Q7 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q7 is the one the claim turns on.</t>
+        </is>
+      </c>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>At Q7, select nothing at all, then submit.</t>
+        </is>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7  (refused at Q7; respondent stays put)</t>
+        </is>
+      </c>
+      <c r="S36" s="6" t="inlineStr">
+        <is>
+          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7</t>
+        </is>
+      </c>
+      <c r="T36" s="6" t="inlineStr">
+        <is>
           <t>Q6</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
-        <is>
-          <t>TC-FT30</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>FOCUSED</t>
-        </is>
-      </c>
-      <c r="E36" s="6" t="inlineStr">
-        <is>
-          <t>9. Rule Interaction</t>
-        </is>
-      </c>
-      <c r="F36" s="6" t="inlineStr">
-        <is>
-          <t>1. Flow / Routing</t>
-        </is>
-      </c>
-      <c r="G36" s="7" t="inlineStr">
-        <is>
-          <t>P03</t>
-        </is>
-      </c>
-      <c r="H36" s="6" t="inlineStr">
-        <is>
-          <t>Q6 is shown and reflects its dependency on Q5 at the same time</t>
-        </is>
-      </c>
-      <c r="I36" s="6" t="inlineStr">
-        <is>
-          <t>Prove Q6 is shown by its display rule and simultaneously reflects its dependency on Q5. Each mechanism can be correct alone and still disagree together.</t>
-        </is>
-      </c>
-      <c r="J36" s="6" t="inlineStr">
-        <is>
-          <t>Individually correct rules can combine into behaviour neither one describes on its own.</t>
-        </is>
-      </c>
-      <c r="K36" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="L36" s="6" t="inlineStr">
-        <is>
-          <t>Travel path P03 (Completing respondent — Q5=Yes) as far as Q6.</t>
-        </is>
-      </c>
-      <c r="M36" s="6" t="inlineStr">
-        <is>
-          <t>FRESH_RESPONDENT</t>
-        </is>
-      </c>
-      <c r="N36" s="6" t="inlineStr">
-        <is>
-          <t>S1 = Yes; S2 = Yes; Q1 = In person; Q2 = Very poor; Q3 = Very poor; Q4 = Content relevance; Q5 = Yes
-then: At Q6, type “xxxxxxxxxx”, then submit.</t>
-        </is>
-      </c>
-      <c r="O36" s="6" t="inlineStr">
-        <is>
-          <t>VALID_TYPICAL for every answer</t>
-        </is>
-      </c>
-      <c r="P36" s="6" t="inlineStr">
-        <is>
-          <t>Every answer before Q6 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q6 is the one the claim turns on.</t>
-        </is>
-      </c>
-      <c r="Q36" s="6" t="inlineStr">
-        <is>
-          <t>At Q6, type “xxxxxxxxxx”, then submit.</t>
-        </is>
-      </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
-        </is>
-      </c>
-      <c r="S36" s="6" t="inlineStr">
-        <is>
-          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
-        </is>
-      </c>
-      <c r="T36" s="6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
       <c r="U36" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="V36" s="6" t="inlineStr">
         <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
+          <t>No forward navigation - the same question must reappear.</t>
         </is>
       </c>
       <c r="W36" s="6" t="inlineStr">
         <is>
-          <t>1. Q6 is on screen
-2. Q6's wording includes: Yes</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q7</t>
         </is>
       </c>
       <c r="X36" s="6" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>Not reached - the respondent cannot progress</t>
         </is>
       </c>
       <c r="Y36" s="6" t="inlineStr">
@@ -6232,8 +6236,7 @@
       </c>
       <c r="Z36" s="6" t="inlineStr">
         <is>
-          <t>Q6 | Please describe the main problem. | text | — | Show if: Q5 == 'Yes'
-Validate: {"min_length": 10, "max_length": 500}</t>
+          <t>Q7 | How likely are you to recommend this service? | single | 0; 1; 2; 3; 4; 5; 6; 7; 8; 9; 10 | Always show</t>
         </is>
       </c>
       <c r="AA36" s="6" t="inlineStr">
@@ -6253,7 +6256,7 @@
       </c>
       <c r="AD36" s="6" t="inlineStr">
         <is>
-          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
         </is>
       </c>
       <c r="AE36" s="6" t="inlineStr">
@@ -6268,105 +6271,105 @@
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
+          <t>Q8</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>TC-FT31</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>FOCUSED</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>1. Flow / Routing</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>Q8 accepts a normal answer and the survey moves on</t>
+        </is>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>Prove that answering Q8 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
+        </is>
+      </c>
+      <c r="J37" s="6" t="inlineStr">
+        <is>
+          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
+        </is>
+      </c>
+      <c r="K37" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L37" s="6" t="inlineStr">
+        <is>
+          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q8.</t>
+        </is>
+      </c>
+      <c r="M37" s="6" t="inlineStr">
+        <is>
+          <t>FRESH_RESPONDENT</t>
+        </is>
+      </c>
+      <c r="N37" s="6" t="inlineStr">
+        <is>
+          <t>S1 = Yes; S2 = Yes; Q1 = In person; Q2 = Very poor; Q3 = Very poor; Q4 = Content relevance; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
+then: Answer through the whole survey as listed, then observe where it ends.</t>
+        </is>
+      </c>
+      <c r="O37" s="6" t="inlineStr">
+        <is>
+          <t>VALID_TYPICAL for every answer</t>
+        </is>
+      </c>
+      <c r="P37" s="6" t="inlineStr">
+        <is>
+          <t>Every answer before Q8 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q8 is the one the claim turns on.</t>
+        </is>
+      </c>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>Answer through the whole survey as listed, then observe where it ends.</t>
+        </is>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
+        </is>
+      </c>
+      <c r="S37" s="6" t="inlineStr">
+        <is>
+          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
+        </is>
+      </c>
+      <c r="T37" s="6" t="inlineStr">
+        <is>
           <t>Q6</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>TC-FT31</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>FOCUSED</t>
-        </is>
-      </c>
-      <c r="E37" s="6" t="inlineStr">
-        <is>
-          <t>2. Input Validation</t>
-        </is>
-      </c>
-      <c r="F37" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G37" s="7" t="inlineStr">
-        <is>
-          <t>P03</t>
-        </is>
-      </c>
-      <c r="H37" s="6" t="inlineStr">
-        <is>
-          <t>Q6 rejects an invalid answer</t>
-        </is>
-      </c>
-      <c r="I37" s="6" t="inlineStr">
-        <is>
-          <t>Prove Q6 refuses an answer that breaks its stated rule. The rule is: at least 10 characters; at most 500 characters</t>
-        </is>
-      </c>
-      <c r="J37" s="6" t="inlineStr">
-        <is>
-          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
-        </is>
-      </c>
-      <c r="K37" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="L37" s="6" t="inlineStr">
-        <is>
-          <t>Travel path P03 (Completing respondent — Q5=Yes) as far as Q6.</t>
-        </is>
-      </c>
-      <c r="M37" s="6" t="inlineStr">
-        <is>
-          <t>FRESH_RESPONDENT</t>
-        </is>
-      </c>
-      <c r="N37" s="6" t="inlineStr">
-        <is>
-          <t>S1 = Yes; S2 = Yes; Q1 = In person; Q2 = Very poor; Q3 = Very poor; Q4 = Content relevance; Q5 = Yes
-then: At Q6, type a 500-character answer, then submit.</t>
-        </is>
-      </c>
-      <c r="O37" s="6" t="inlineStr">
-        <is>
-          <t>VALID_TYPICAL for every answer</t>
-        </is>
-      </c>
-      <c r="P37" s="6" t="inlineStr">
-        <is>
-          <t>Every answer before Q6 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q6 is the one the claim turns on.</t>
-        </is>
-      </c>
-      <c r="Q37" s="6" t="inlineStr">
-        <is>
-          <t>At Q6, type a 500-character answer, then submit.</t>
-        </is>
-      </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
-        </is>
-      </c>
-      <c r="S37" s="6" t="inlineStr">
-        <is>
-          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
-        </is>
-      </c>
-      <c r="T37" s="6" t="inlineStr">
+      <c r="U37" s="6" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="U37" s="6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
       <c r="V37" s="6" t="inlineStr">
         <is>
           <t>Each listed question is followed immediately by the next in the sequence.</t>
@@ -6374,7 +6377,8 @@
       </c>
       <c r="W37" s="6" t="inlineStr">
         <is>
-          <t>1. the survey ACCEPTS the answer and moves on</t>
+          <t>1. Q8 is on screen
+2. the respondent reaches the normal thank-you page</t>
         </is>
       </c>
       <c r="X37" s="6" t="inlineStr">
@@ -6389,13 +6393,13 @@
       </c>
       <c r="Z37" s="6" t="inlineStr">
         <is>
-          <t>Q6 | Please describe the main problem. | text | — | Show if: Q5 == 'Yes'
-Validate: {"min_length": 10, "max_length": 500}</t>
+          <t>Q8 | What is the single most important improvement you would suggest? | text | — | Validate: {"max_length": 500}
+Optional</t>
         </is>
       </c>
       <c r="AA37" s="6" t="inlineStr">
         <is>
-          <t>Derived by rule from the questionnaire's own tables.</t>
+          <t>QRE explicit - stated directly in the questionnaire.</t>
         </is>
       </c>
       <c r="AB37" s="8" t="inlineStr">
@@ -6410,7 +6414,7 @@
       </c>
       <c r="AD37" s="6" t="inlineStr">
         <is>
-          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE37" s="6" t="inlineStr">
@@ -6425,105 +6429,105 @@
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
+          <t>Q8</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>TC-FT32</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>FOCUSED</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>2. Input Validation</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>Q8 accepts a valid answer</t>
+        </is>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>Prove Q8 accepts an answer that obeys its stated rule. The rule is: at most 500 characters</t>
+        </is>
+      </c>
+      <c r="J38" s="6" t="inlineStr">
+        <is>
+          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
+        </is>
+      </c>
+      <c r="K38" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L38" s="6" t="inlineStr">
+        <is>
+          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q8.</t>
+        </is>
+      </c>
+      <c r="M38" s="6" t="inlineStr">
+        <is>
+          <t>FRESH_RESPONDENT</t>
+        </is>
+      </c>
+      <c r="N38" s="6" t="inlineStr">
+        <is>
+          <t>S1 = Yes; S2 = Yes; Q1 = In person; Q2 = Very poor; Q3 = Very poor; Q4 = Content relevance; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
+then: At Q8, type “x”, then submit.</t>
+        </is>
+      </c>
+      <c r="O38" s="6" t="inlineStr">
+        <is>
+          <t>VALID_BOUNDARY</t>
+        </is>
+      </c>
+      <c r="P38" s="6" t="inlineStr">
+        <is>
+          <t>Every answer before Q8 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q8 is the one the claim turns on.</t>
+        </is>
+      </c>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>At Q8, type “x”, then submit.</t>
+        </is>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
+        </is>
+      </c>
+      <c r="S38" s="6" t="inlineStr">
+        <is>
+          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
+        </is>
+      </c>
+      <c r="T38" s="6" t="inlineStr">
+        <is>
           <t>Q6</t>
         </is>
       </c>
-      <c r="C38" s="7" t="inlineStr">
-        <is>
-          <t>TC-FT32</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>FOCUSED</t>
-        </is>
-      </c>
-      <c r="E38" s="6" t="inlineStr">
-        <is>
-          <t>2. Input Validation</t>
-        </is>
-      </c>
-      <c r="F38" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G38" s="7" t="inlineStr">
-        <is>
-          <t>P03</t>
-        </is>
-      </c>
-      <c r="H38" s="6" t="inlineStr">
-        <is>
-          <t>Q6 rejects an invalid answer</t>
-        </is>
-      </c>
-      <c r="I38" s="6" t="inlineStr">
-        <is>
-          <t>Prove Q6 refuses an answer that breaks its stated rule. The rule is: at least 10 characters; at most 500 characters</t>
-        </is>
-      </c>
-      <c r="J38" s="6" t="inlineStr">
-        <is>
-          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
-        </is>
-      </c>
-      <c r="K38" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="L38" s="6" t="inlineStr">
-        <is>
-          <t>Travel path P03 (Completing respondent — Q5=Yes) as far as Q6.</t>
-        </is>
-      </c>
-      <c r="M38" s="6" t="inlineStr">
-        <is>
-          <t>FRESH_RESPONDENT</t>
-        </is>
-      </c>
-      <c r="N38" s="6" t="inlineStr">
-        <is>
-          <t>S1 = Yes; S2 = Yes; Q1 = In person; Q2 = Very poor; Q3 = Very poor; Q4 = Content relevance; Q5 = Yes
-then: At Q6, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
-        </is>
-      </c>
-      <c r="O38" s="6" t="inlineStr">
-        <is>
-          <t>VALID_TYPICAL for every answer</t>
-        </is>
-      </c>
-      <c r="P38" s="6" t="inlineStr">
-        <is>
-          <t>Every answer before Q6 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q6 is the one the claim turns on.</t>
-        </is>
-      </c>
-      <c r="Q38" s="6" t="inlineStr">
-        <is>
-          <t>At Q6, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
-        </is>
-      </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
-        </is>
-      </c>
-      <c r="S38" s="6" t="inlineStr">
-        <is>
-          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
-        </is>
-      </c>
-      <c r="T38" s="6" t="inlineStr">
+      <c r="U38" s="6" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="U38" s="6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
       <c r="V38" s="6" t="inlineStr">
         <is>
           <t>Each listed question is followed immediately by the next in the sequence.</t>
@@ -6546,13 +6550,13 @@
       </c>
       <c r="Z38" s="6" t="inlineStr">
         <is>
-          <t>Q6 | Please describe the main problem. | text | — | Show if: Q5 == 'Yes'
-Validate: {"min_length": 10, "max_length": 500}</t>
+          <t>Q8 | What is the single most important improvement you would suggest? | text | — | Validate: {"max_length": 500}
+Optional</t>
         </is>
       </c>
       <c r="AA38" s="6" t="inlineStr">
         <is>
-          <t>Derived by rule from the questionnaire's own tables.</t>
+          <t>QRE explicit - stated directly in the questionnaire.</t>
         </is>
       </c>
       <c r="AB38" s="8" t="inlineStr">
@@ -6582,155 +6586,155 @@
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
+          <t>Q8</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>TC-FT33</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>FOCUSED</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>2. Input Validation</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>10. Negative / Robustness</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>Q8 rejects an invalid answer</t>
+        </is>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>Prove Q8 refuses an answer that breaks its stated rule. The rule is: at most 500 characters</t>
+        </is>
+      </c>
+      <c r="J39" s="6" t="inlineStr">
+        <is>
+          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
+        </is>
+      </c>
+      <c r="K39" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L39" s="6" t="inlineStr">
+        <is>
+          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q8.</t>
+        </is>
+      </c>
+      <c r="M39" s="6" t="inlineStr">
+        <is>
+          <t>FRESH_RESPONDENT</t>
+        </is>
+      </c>
+      <c r="N39" s="6" t="inlineStr">
+        <is>
+          <t>S1 = Yes; S2 = Yes; Q1 = In person; Q2 = Very poor; Q3 = Very poor; Q4 = Content relevance; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
+then: At Q8, type a 501-character answer, then submit.</t>
+        </is>
+      </c>
+      <c r="O39" s="6" t="inlineStr">
+        <is>
+          <t>INVALID_BOUNDARY</t>
+        </is>
+      </c>
+      <c r="P39" s="6" t="inlineStr">
+        <is>
+          <t>Every answer before Q8 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q8 is the one the claim turns on.</t>
+        </is>
+      </c>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>At Q8, type a 501-character answer, then submit.</t>
+        </is>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8  (refused at Q8; respondent stays put)</t>
+        </is>
+      </c>
+      <c r="S39" s="6" t="inlineStr">
+        <is>
+          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
+        </is>
+      </c>
+      <c r="T39" s="6" t="inlineStr">
+        <is>
           <t>Q6</t>
         </is>
       </c>
-      <c r="C39" s="7" t="inlineStr">
-        <is>
-          <t>TC-FT33</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>FOCUSED</t>
-        </is>
-      </c>
-      <c r="E39" s="6" t="inlineStr">
-        <is>
-          <t>2. Input Validation</t>
-        </is>
-      </c>
-      <c r="F39" s="6" t="inlineStr">
+      <c r="U39" s="6" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="V39" s="6" t="inlineStr">
+        <is>
+          <t>No forward navigation - the same question must reappear.</t>
+        </is>
+      </c>
+      <c r="W39" s="6" t="inlineStr">
+        <is>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q8</t>
+        </is>
+      </c>
+      <c r="X39" s="6" t="inlineStr">
+        <is>
+          <t>Not reached - the respondent cannot progress</t>
+        </is>
+      </c>
+      <c r="Y39" s="6" t="inlineStr">
+        <is>
+          <t>Page render per question, plus the ordered sequence log and any validation message shown.</t>
+        </is>
+      </c>
+      <c r="Z39" s="6" t="inlineStr">
+        <is>
+          <t>Q8 | What is the single most important improvement you would suggest? | text | — | Validate: {"max_length": 500}
+Optional</t>
+        </is>
+      </c>
+      <c r="AA39" s="6" t="inlineStr">
+        <is>
+          <t>QRE explicit - stated directly in the questionnaire.</t>
+        </is>
+      </c>
+      <c r="AB39" s="8" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
+        </is>
+      </c>
+      <c r="AC39" s="8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AD39" s="6" t="inlineStr">
+        <is>
+          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+        </is>
+      </c>
+      <c r="AE39" s="6" t="inlineStr">
         <is>
           <t>-</t>
-        </is>
-      </c>
-      <c r="G39" s="7" t="inlineStr">
-        <is>
-          <t>P03</t>
-        </is>
-      </c>
-      <c r="H39" s="6" t="inlineStr">
-        <is>
-          <t>Q6 allows a blank answer, being optional</t>
-        </is>
-      </c>
-      <c r="I39" s="6" t="inlineStr">
-        <is>
-          <t>Prove Q6 lets the respondent through with no answer, because the questionnaire marks it optional.</t>
-        </is>
-      </c>
-      <c r="J39" s="6" t="inlineStr">
-        <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
-        </is>
-      </c>
-      <c r="K39" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="L39" s="6" t="inlineStr">
-        <is>
-          <t>Travel path P03 (Completing respondent — Q5=Yes) as far as Q6.</t>
-        </is>
-      </c>
-      <c r="M39" s="6" t="inlineStr">
-        <is>
-          <t>FRESH_RESPONDENT</t>
-        </is>
-      </c>
-      <c r="N39" s="6" t="inlineStr">
-        <is>
-          <t>S1 = Yes; S2 = Yes; Q1 = In person; Q2 = Very poor; Q3 = Very poor; Q4 = Content relevance; Q5 = Yes
-then: At Q6, type 3 spaces and nothing else, then submit.</t>
-        </is>
-      </c>
-      <c r="O39" s="6" t="inlineStr">
-        <is>
-          <t>VALID_TYPICAL for every answer</t>
-        </is>
-      </c>
-      <c r="P39" s="6" t="inlineStr">
-        <is>
-          <t>Every answer before Q6 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q6 is the one the claim turns on.</t>
-        </is>
-      </c>
-      <c r="Q39" s="6" t="inlineStr">
-        <is>
-          <t>At Q6, type 3 spaces and nothing else, then submit.</t>
-        </is>
-      </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6  (refused at Q6; respondent stays put)</t>
-        </is>
-      </c>
-      <c r="S39" s="6" t="inlineStr">
-        <is>
-          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6</t>
-        </is>
-      </c>
-      <c r="T39" s="6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="U39" s="6" t="inlineStr">
-        <is>
-          <t>Q7, Q8</t>
-        </is>
-      </c>
-      <c r="V39" s="6" t="inlineStr">
-        <is>
-          <t>No forward navigation - the same question must reappear.</t>
-        </is>
-      </c>
-      <c r="W39" s="6" t="inlineStr">
-        <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q6</t>
-        </is>
-      </c>
-      <c r="X39" s="6" t="inlineStr">
-        <is>
-          <t>Not reached - the respondent cannot progress</t>
-        </is>
-      </c>
-      <c r="Y39" s="6" t="inlineStr">
-        <is>
-          <t>Page render per question, plus the ordered sequence log and any validation message shown.</t>
-        </is>
-      </c>
-      <c r="Z39" s="6" t="inlineStr">
-        <is>
-          <t>Q6 | Please describe the main problem. | text | — | Show if: Q5 == 'Yes'
-Validate: {"min_length": 10, "max_length": 500}</t>
-        </is>
-      </c>
-      <c r="AA39" s="6" t="inlineStr">
-        <is>
-          <t>Derived by rule from the questionnaire's own tables.</t>
-        </is>
-      </c>
-      <c r="AB39" s="10" t="inlineStr">
-        <is>
-          <t>PROVISIONAL</t>
-        </is>
-      </c>
-      <c r="AC39" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="AD39" s="6" t="inlineStr">
-        <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
-        </is>
-      </c>
-      <c r="AE39" s="6" t="inlineStr">
-        <is>
-          <t>Leans on an unconfirmed reading: whitespace_is_an_answer</t>
         </is>
       </c>
     </row>
@@ -6740,7 +6744,7 @@
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>Q7</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
@@ -6755,7 +6759,7 @@
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
@@ -6770,27 +6774,27 @@
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>Q7 accepts a normal answer and the survey moves on</t>
+          <t>Q8 allows a blank answer, being optional</t>
         </is>
       </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
-          <t>Prove that answering Q7 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
+          <t>Prove Q8 lets the respondent through with no answer, because the questionnaire marks it optional.</t>
         </is>
       </c>
       <c r="J40" s="6" t="inlineStr">
         <is>
-          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
         </is>
       </c>
       <c r="K40" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L40" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q7.</t>
+          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q8.</t>
         </is>
       </c>
       <c r="M40" s="6" t="inlineStr">
@@ -6801,22 +6805,22 @@
       <c r="N40" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; Q1 = In person; Q2 = Very poor; Q3 = Very poor; Q4 = Content relevance; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
-then: Answer through the whole survey as listed, then observe where it ends.</t>
+then: At Q8, type nothing, then submit.</t>
         </is>
       </c>
       <c r="O40" s="6" t="inlineStr">
         <is>
-          <t>VALID_TYPICAL for every answer</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="P40" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q7 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q7 is the one the claim turns on.</t>
+          <t>Every answer before Q8 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q8 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q40" s="6" t="inlineStr">
         <is>
-          <t>Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>At Q8, type nothing, then submit.</t>
         </is>
       </c>
       <c r="R40" s="6" t="inlineStr">
@@ -6846,8 +6850,7 @@
       </c>
       <c r="W40" s="6" t="inlineStr">
         <is>
-          <t>1. Q7 is on screen
-2. the next question shown is Q8</t>
+          <t>1. the survey ACCEPTS the answer and moves on</t>
         </is>
       </c>
       <c r="X40" s="6" t="inlineStr">
@@ -6862,7 +6865,8 @@
       </c>
       <c r="Z40" s="6" t="inlineStr">
         <is>
-          <t>Q7 | How likely are you to recommend this service? | single | 0; 1; 2; 3; 4; 5; 6; 7; 8; 9; 10 | Always show</t>
+          <t>Q8 | What is the single most important improvement you would suggest? | text | — | Validate: {"max_length": 500}
+Optional</t>
         </is>
       </c>
       <c r="AA40" s="6" t="inlineStr">
@@ -6882,7 +6886,7 @@
       </c>
       <c r="AD40" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
         </is>
       </c>
       <c r="AE40" s="6" t="inlineStr">
@@ -6897,7 +6901,7 @@
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>Q7</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
@@ -6917,7 +6921,7 @@
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>10. Negative / Robustness</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
@@ -6927,27 +6931,27 @@
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
-          <t>Q7 blocks a blank answer</t>
+          <t>Q8 rejects an invalid answer</t>
         </is>
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
-          <t>Prove Q7 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
+          <t>Prove Q8 refuses an answer that breaks its stated rule. The rule is: at most 500 characters</t>
         </is>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
         </is>
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L41" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q7.</t>
+          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q8.</t>
         </is>
       </c>
       <c r="M41" s="6" t="inlineStr">
@@ -6957,33 +6961,33 @@
       </c>
       <c r="N41" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; Q1 = In person; Q2 = Very poor; Q3 = Very poor; Q4 = Content relevance; Q5 = Yes; Q6 = xxxxxxxxxx
-then: At Q7, select nothing at all, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; Q1 = In person; Q2 = Very poor; Q3 = Very poor; Q4 = Content relevance; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
+then: At Q8, type a 500-character answer, then submit.</t>
         </is>
       </c>
       <c r="O41" s="6" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P41" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q7 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q7 is the one the claim turns on.</t>
+          <t>Every answer before Q8 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q8 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q41" s="6" t="inlineStr">
         <is>
-          <t>At Q7, select nothing at all, then submit.</t>
+          <t>At Q8, type a 500-character answer, then submit.</t>
         </is>
       </c>
       <c r="R41" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7  (refused at Q7; respondent stays put)</t>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
         </is>
       </c>
       <c r="S41" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7</t>
+          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
         </is>
       </c>
       <c r="T41" s="6" t="inlineStr">
@@ -6993,23 +6997,22 @@
       </c>
       <c r="U41" s="6" t="inlineStr">
         <is>
-          <t>Q8</t>
+          <t>none</t>
         </is>
       </c>
       <c r="V41" s="6" t="inlineStr">
         <is>
-          <t>No forward navigation - the same question must reappear.</t>
+          <t>Each listed question is followed immediately by the next in the sequence.</t>
         </is>
       </c>
       <c r="W41" s="6" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q7</t>
+          <t>1. the survey ACCEPTS the answer and moves on</t>
         </is>
       </c>
       <c r="X41" s="6" t="inlineStr">
         <is>
-          <t>Not reached - the respondent cannot progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="Y41" s="6" t="inlineStr">
@@ -7019,7 +7022,8 @@
       </c>
       <c r="Z41" s="6" t="inlineStr">
         <is>
-          <t>Q7 | How likely are you to recommend this service? | single | 0; 1; 2; 3; 4; 5; 6; 7; 8; 9; 10 | Always show</t>
+          <t>Q8 | What is the single most important improvement you would suggest? | text | — | Validate: {"max_length": 500}
+Optional</t>
         </is>
       </c>
       <c r="AA41" s="6" t="inlineStr">
@@ -7039,7 +7043,7 @@
       </c>
       <c r="AD41" s="6" t="inlineStr">
         <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE41" s="6" t="inlineStr">
@@ -7069,7 +7073,7 @@
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
@@ -7084,17 +7088,17 @@
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>Q8 accepts a normal answer and the survey moves on</t>
+          <t>Q8 rejects an invalid answer</t>
         </is>
       </c>
       <c r="I42" s="6" t="inlineStr">
         <is>
-          <t>Prove that answering Q8 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
+          <t>Prove Q8 refuses an answer that breaks its stated rule. The rule is: at most 500 characters</t>
         </is>
       </c>
       <c r="J42" s="6" t="inlineStr">
         <is>
-          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
+          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
         </is>
       </c>
       <c r="K42" s="6" t="inlineStr">
@@ -7115,7 +7119,7 @@
       <c r="N42" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; Q1 = In person; Q2 = Very poor; Q3 = Very poor; Q4 = Content relevance; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
-then: Answer through the whole survey as listed, then observe where it ends.</t>
+then: At Q8, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
         </is>
       </c>
       <c r="O42" s="6" t="inlineStr">
@@ -7130,7 +7134,7 @@
       </c>
       <c r="Q42" s="6" t="inlineStr">
         <is>
-          <t>Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>At Q8, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
         </is>
       </c>
       <c r="R42" s="6" t="inlineStr">
@@ -7160,8 +7164,7 @@
       </c>
       <c r="W42" s="6" t="inlineStr">
         <is>
-          <t>1. Q8 is on screen
-2. the respondent reaches the normal thank-you page</t>
+          <t>1. the survey ACCEPTS the answer and moves on</t>
         </is>
       </c>
       <c r="X42" s="6" t="inlineStr">
@@ -7197,7 +7200,7 @@
       </c>
       <c r="AD42" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE42" s="6" t="inlineStr">
@@ -7242,22 +7245,22 @@
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>Q8 accepts a valid answer</t>
+          <t>Q8 allows a blank answer, being optional</t>
         </is>
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
-          <t>Prove Q8 accepts an answer that obeys its stated rule. The rule is: at most 500 characters</t>
+          <t>Prove Q8 lets the respondent through with no answer, because the questionnaire marks it optional.</t>
         </is>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
         </is>
       </c>
       <c r="K43" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L43" s="6" t="inlineStr">
@@ -7273,12 +7276,12 @@
       <c r="N43" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; Q1 = In person; Q2 = Very poor; Q3 = Very poor; Q4 = Content relevance; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
-then: At Q8, type “x”, then submit.</t>
+then: At Q8, type 3 spaces and nothing else, then submit.</t>
         </is>
       </c>
       <c r="O43" s="6" t="inlineStr">
         <is>
-          <t>VALID_BOUNDARY</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P43" s="6" t="inlineStr">
@@ -7288,7 +7291,7 @@
       </c>
       <c r="Q43" s="6" t="inlineStr">
         <is>
-          <t>At Q8, type “x”, then submit.</t>
+          <t>At Q8, type 3 spaces and nothing else, then submit.</t>
         </is>
       </c>
       <c r="R43" s="6" t="inlineStr">
@@ -7342,9 +7345,9 @@
           <t>QRE explicit - stated directly in the questionnaire.</t>
         </is>
       </c>
-      <c r="AB43" s="8" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
+      <c r="AB43" s="10" t="inlineStr">
+        <is>
+          <t>PROVISIONAL</t>
         </is>
       </c>
       <c r="AC43" s="8" t="inlineStr">
@@ -7354,12 +7357,12 @@
       </c>
       <c r="AD43" s="6" t="inlineStr">
         <is>
-          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
         </is>
       </c>
       <c r="AE43" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Leans on an unconfirmed reading: whitespace_is_an_answer</t>
         </is>
       </c>
     </row>
@@ -7369,57 +7372,57 @@
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>Q8</t>
+          <t>whole survey</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>TC-FT38</t>
+          <t>TC-RT03</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>FOCUSED</t>
+          <t>ROUTE</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>2. Input Validation</t>
+          <t>6. Termination / Disposition</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>10. Negative / Robustness</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P03</t>
         </is>
       </c>
       <c r="H44" s="6" t="inlineStr">
         <is>
-          <t>Q8 rejects an invalid answer</t>
+          <t>End-to-end journey: COMPLETE by way of routing</t>
         </is>
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
-          <t>Prove Q8 refuses an answer that breaks its stated rule. The rule is: at most 500 characters</t>
+          <t>Prove that a respondent answering as listed is shown exactly this sequence of questions, in this order, and ends at COMPLETE by way of the routing, checked at ?. Condition: . They should then see: “Thank you. Your response has been recorded.”</t>
         </is>
       </c>
       <c r="J44" s="6" t="inlineStr">
         <is>
-          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
+          <t>Screening someone out incorrectly loses a valid respondent and the money spent recruiting them. Failing to screen someone out puts the wrong person in the sample.</t>
         </is>
       </c>
       <c r="K44" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="L44" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q8.</t>
+          <t>Travel path P03 (Completing respondent — Q5=Yes) as far as the end.</t>
         </is>
       </c>
       <c r="M44" s="6" t="inlineStr">
@@ -7428,878 +7431,92 @@
         </is>
       </c>
       <c r="N44" s="6" t="inlineStr">
-        <is>
-          <t>S1 = Yes; S2 = Yes; Q1 = In person; Q2 = Very poor; Q3 = Very poor; Q4 = Content relevance; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
-then: At Q8, type a 501-character answer, then submit.</t>
-        </is>
-      </c>
-      <c r="O44" s="6" t="inlineStr">
-        <is>
-          <t>INVALID_BOUNDARY</t>
-        </is>
-      </c>
-      <c r="P44" s="6" t="inlineStr">
-        <is>
-          <t>Every answer before Q8 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q8 is the one the claim turns on.</t>
-        </is>
-      </c>
-      <c r="Q44" s="6" t="inlineStr">
-        <is>
-          <t>At Q8, type a 501-character answer, then submit.</t>
-        </is>
-      </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8  (refused at Q8; respondent stays put)</t>
-        </is>
-      </c>
-      <c r="S44" s="6" t="inlineStr">
-        <is>
-          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
-        </is>
-      </c>
-      <c r="T44" s="6" t="inlineStr">
-        <is>
-          <t>Q6</t>
-        </is>
-      </c>
-      <c r="U44" s="6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="V44" s="6" t="inlineStr">
-        <is>
-          <t>No forward navigation - the same question must reappear.</t>
-        </is>
-      </c>
-      <c r="W44" s="6" t="inlineStr">
-        <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q8</t>
-        </is>
-      </c>
-      <c r="X44" s="6" t="inlineStr">
-        <is>
-          <t>Not reached - the respondent cannot progress</t>
-        </is>
-      </c>
-      <c r="Y44" s="6" t="inlineStr">
-        <is>
-          <t>Page render per question, plus the ordered sequence log and any validation message shown.</t>
-        </is>
-      </c>
-      <c r="Z44" s="6" t="inlineStr">
-        <is>
-          <t>Q8 | What is the single most important improvement you would suggest? | text | — | Validate: {"max_length": 500}
-Optional</t>
-        </is>
-      </c>
-      <c r="AA44" s="6" t="inlineStr">
-        <is>
-          <t>QRE explicit - stated directly in the questionnaire.</t>
-        </is>
-      </c>
-      <c r="AB44" s="8" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
-        </is>
-      </c>
-      <c r="AC44" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="AD44" s="6" t="inlineStr">
-        <is>
-          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
-        </is>
-      </c>
-      <c r="AE44" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="B45" s="9" t="inlineStr">
-        <is>
-          <t>Q8</t>
-        </is>
-      </c>
-      <c r="C45" s="7" t="inlineStr">
-        <is>
-          <t>TC-FT39</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>FOCUSED</t>
-        </is>
-      </c>
-      <c r="E45" s="6" t="inlineStr">
-        <is>
-          <t>2. Input Validation</t>
-        </is>
-      </c>
-      <c r="F45" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G45" s="7" t="inlineStr">
-        <is>
-          <t>P04</t>
-        </is>
-      </c>
-      <c r="H45" s="6" t="inlineStr">
-        <is>
-          <t>Q8 allows a blank answer, being optional</t>
-        </is>
-      </c>
-      <c r="I45" s="6" t="inlineStr">
-        <is>
-          <t>Prove Q8 lets the respondent through with no answer, because the questionnaire marks it optional.</t>
-        </is>
-      </c>
-      <c r="J45" s="6" t="inlineStr">
-        <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
-        </is>
-      </c>
-      <c r="K45" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="L45" s="6" t="inlineStr">
-        <is>
-          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q8.</t>
-        </is>
-      </c>
-      <c r="M45" s="6" t="inlineStr">
-        <is>
-          <t>FRESH_RESPONDENT</t>
-        </is>
-      </c>
-      <c r="N45" s="6" t="inlineStr">
-        <is>
-          <t>S1 = Yes; S2 = Yes; Q1 = In person; Q2 = Very poor; Q3 = Very poor; Q4 = Content relevance; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
-then: At Q8, type nothing, then submit.</t>
-        </is>
-      </c>
-      <c r="O45" s="6" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="P45" s="6" t="inlineStr">
-        <is>
-          <t>Every answer before Q8 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q8 is the one the claim turns on.</t>
-        </is>
-      </c>
-      <c r="Q45" s="6" t="inlineStr">
-        <is>
-          <t>At Q8, type nothing, then submit.</t>
-        </is>
-      </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
-        </is>
-      </c>
-      <c r="S45" s="6" t="inlineStr">
-        <is>
-          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
-        </is>
-      </c>
-      <c r="T45" s="6" t="inlineStr">
-        <is>
-          <t>Q6</t>
-        </is>
-      </c>
-      <c r="U45" s="6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="V45" s="6" t="inlineStr">
-        <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
-        </is>
-      </c>
-      <c r="W45" s="6" t="inlineStr">
-        <is>
-          <t>1. the survey ACCEPTS the answer and moves on</t>
-        </is>
-      </c>
-      <c r="X45" s="6" t="inlineStr">
-        <is>
-          <t>COMPLETE</t>
-        </is>
-      </c>
-      <c r="Y45" s="6" t="inlineStr">
-        <is>
-          <t>Page render per question, plus the ordered sequence log and any validation message shown.</t>
-        </is>
-      </c>
-      <c r="Z45" s="6" t="inlineStr">
-        <is>
-          <t>Q8 | What is the single most important improvement you would suggest? | text | — | Validate: {"max_length": 500}
-Optional</t>
-        </is>
-      </c>
-      <c r="AA45" s="6" t="inlineStr">
-        <is>
-          <t>QRE explicit - stated directly in the questionnaire.</t>
-        </is>
-      </c>
-      <c r="AB45" s="8" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
-        </is>
-      </c>
-      <c r="AC45" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="AD45" s="6" t="inlineStr">
-        <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
-        </is>
-      </c>
-      <c r="AE45" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="B46" s="9" t="inlineStr">
-        <is>
-          <t>Q8</t>
-        </is>
-      </c>
-      <c r="C46" s="7" t="inlineStr">
-        <is>
-          <t>TC-FT40</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
-          <t>FOCUSED</t>
-        </is>
-      </c>
-      <c r="E46" s="6" t="inlineStr">
-        <is>
-          <t>2. Input Validation</t>
-        </is>
-      </c>
-      <c r="F46" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G46" s="7" t="inlineStr">
-        <is>
-          <t>P04</t>
-        </is>
-      </c>
-      <c r="H46" s="6" t="inlineStr">
-        <is>
-          <t>Q8 rejects an invalid answer</t>
-        </is>
-      </c>
-      <c r="I46" s="6" t="inlineStr">
-        <is>
-          <t>Prove Q8 refuses an answer that breaks its stated rule. The rule is: at most 500 characters</t>
-        </is>
-      </c>
-      <c r="J46" s="6" t="inlineStr">
-        <is>
-          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
-        </is>
-      </c>
-      <c r="K46" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="L46" s="6" t="inlineStr">
-        <is>
-          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q8.</t>
-        </is>
-      </c>
-      <c r="M46" s="6" t="inlineStr">
-        <is>
-          <t>FRESH_RESPONDENT</t>
-        </is>
-      </c>
-      <c r="N46" s="6" t="inlineStr">
-        <is>
-          <t>S1 = Yes; S2 = Yes; Q1 = In person; Q2 = Very poor; Q3 = Very poor; Q4 = Content relevance; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
-then: At Q8, type a 500-character answer, then submit.</t>
-        </is>
-      </c>
-      <c r="O46" s="6" t="inlineStr">
-        <is>
-          <t>VALID_TYPICAL for every answer</t>
-        </is>
-      </c>
-      <c r="P46" s="6" t="inlineStr">
-        <is>
-          <t>Every answer before Q8 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q8 is the one the claim turns on.</t>
-        </is>
-      </c>
-      <c r="Q46" s="6" t="inlineStr">
-        <is>
-          <t>At Q8, type a 500-character answer, then submit.</t>
-        </is>
-      </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
-        </is>
-      </c>
-      <c r="S46" s="6" t="inlineStr">
-        <is>
-          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
-        </is>
-      </c>
-      <c r="T46" s="6" t="inlineStr">
-        <is>
-          <t>Q6</t>
-        </is>
-      </c>
-      <c r="U46" s="6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="V46" s="6" t="inlineStr">
-        <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
-        </is>
-      </c>
-      <c r="W46" s="6" t="inlineStr">
-        <is>
-          <t>1. the survey ACCEPTS the answer and moves on</t>
-        </is>
-      </c>
-      <c r="X46" s="6" t="inlineStr">
-        <is>
-          <t>COMPLETE</t>
-        </is>
-      </c>
-      <c r="Y46" s="6" t="inlineStr">
-        <is>
-          <t>Page render per question, plus the ordered sequence log and any validation message shown.</t>
-        </is>
-      </c>
-      <c r="Z46" s="6" t="inlineStr">
-        <is>
-          <t>Q8 | What is the single most important improvement you would suggest? | text | — | Validate: {"max_length": 500}
-Optional</t>
-        </is>
-      </c>
-      <c r="AA46" s="6" t="inlineStr">
-        <is>
-          <t>QRE explicit - stated directly in the questionnaire.</t>
-        </is>
-      </c>
-      <c r="AB46" s="8" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
-        </is>
-      </c>
-      <c r="AC46" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="AD46" s="6" t="inlineStr">
-        <is>
-          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
-        </is>
-      </c>
-      <c r="AE46" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="4" t="n">
-        <v>43</v>
-      </c>
-      <c r="B47" s="9" t="inlineStr">
-        <is>
-          <t>Q8</t>
-        </is>
-      </c>
-      <c r="C47" s="7" t="inlineStr">
-        <is>
-          <t>TC-FT41</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>FOCUSED</t>
-        </is>
-      </c>
-      <c r="E47" s="6" t="inlineStr">
-        <is>
-          <t>2. Input Validation</t>
-        </is>
-      </c>
-      <c r="F47" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G47" s="7" t="inlineStr">
-        <is>
-          <t>P04</t>
-        </is>
-      </c>
-      <c r="H47" s="6" t="inlineStr">
-        <is>
-          <t>Q8 rejects an invalid answer</t>
-        </is>
-      </c>
-      <c r="I47" s="6" t="inlineStr">
-        <is>
-          <t>Prove Q8 refuses an answer that breaks its stated rule. The rule is: at most 500 characters</t>
-        </is>
-      </c>
-      <c r="J47" s="6" t="inlineStr">
-        <is>
-          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
-        </is>
-      </c>
-      <c r="K47" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="L47" s="6" t="inlineStr">
-        <is>
-          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q8.</t>
-        </is>
-      </c>
-      <c r="M47" s="6" t="inlineStr">
-        <is>
-          <t>FRESH_RESPONDENT</t>
-        </is>
-      </c>
-      <c r="N47" s="6" t="inlineStr">
-        <is>
-          <t>S1 = Yes; S2 = Yes; Q1 = In person; Q2 = Very poor; Q3 = Very poor; Q4 = Content relevance; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
-then: At Q8, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
-        </is>
-      </c>
-      <c r="O47" s="6" t="inlineStr">
-        <is>
-          <t>VALID_TYPICAL for every answer</t>
-        </is>
-      </c>
-      <c r="P47" s="6" t="inlineStr">
-        <is>
-          <t>Every answer before Q8 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q8 is the one the claim turns on.</t>
-        </is>
-      </c>
-      <c r="Q47" s="6" t="inlineStr">
-        <is>
-          <t>At Q8, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
-        </is>
-      </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
-        </is>
-      </c>
-      <c r="S47" s="6" t="inlineStr">
-        <is>
-          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
-        </is>
-      </c>
-      <c r="T47" s="6" t="inlineStr">
-        <is>
-          <t>Q6</t>
-        </is>
-      </c>
-      <c r="U47" s="6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="V47" s="6" t="inlineStr">
-        <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
-        </is>
-      </c>
-      <c r="W47" s="6" t="inlineStr">
-        <is>
-          <t>1. the survey ACCEPTS the answer and moves on</t>
-        </is>
-      </c>
-      <c r="X47" s="6" t="inlineStr">
-        <is>
-          <t>COMPLETE</t>
-        </is>
-      </c>
-      <c r="Y47" s="6" t="inlineStr">
-        <is>
-          <t>Page render per question, plus the ordered sequence log and any validation message shown.</t>
-        </is>
-      </c>
-      <c r="Z47" s="6" t="inlineStr">
-        <is>
-          <t>Q8 | What is the single most important improvement you would suggest? | text | — | Validate: {"max_length": 500}
-Optional</t>
-        </is>
-      </c>
-      <c r="AA47" s="6" t="inlineStr">
-        <is>
-          <t>QRE explicit - stated directly in the questionnaire.</t>
-        </is>
-      </c>
-      <c r="AB47" s="8" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
-        </is>
-      </c>
-      <c r="AC47" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="AD47" s="6" t="inlineStr">
-        <is>
-          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
-        </is>
-      </c>
-      <c r="AE47" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="4" t="n">
-        <v>44</v>
-      </c>
-      <c r="B48" s="9" t="inlineStr">
-        <is>
-          <t>Q8</t>
-        </is>
-      </c>
-      <c r="C48" s="7" t="inlineStr">
-        <is>
-          <t>TC-FT42</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="inlineStr">
-        <is>
-          <t>FOCUSED</t>
-        </is>
-      </c>
-      <c r="E48" s="6" t="inlineStr">
-        <is>
-          <t>2. Input Validation</t>
-        </is>
-      </c>
-      <c r="F48" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G48" s="7" t="inlineStr">
-        <is>
-          <t>P04</t>
-        </is>
-      </c>
-      <c r="H48" s="6" t="inlineStr">
-        <is>
-          <t>Q8 allows a blank answer, being optional</t>
-        </is>
-      </c>
-      <c r="I48" s="6" t="inlineStr">
-        <is>
-          <t>Prove Q8 lets the respondent through with no answer, because the questionnaire marks it optional.</t>
-        </is>
-      </c>
-      <c r="J48" s="6" t="inlineStr">
-        <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
-        </is>
-      </c>
-      <c r="K48" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="L48" s="6" t="inlineStr">
-        <is>
-          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q8.</t>
-        </is>
-      </c>
-      <c r="M48" s="6" t="inlineStr">
-        <is>
-          <t>FRESH_RESPONDENT</t>
-        </is>
-      </c>
-      <c r="N48" s="6" t="inlineStr">
-        <is>
-          <t>S1 = Yes; S2 = Yes; Q1 = In person; Q2 = Very poor; Q3 = Very poor; Q4 = Content relevance; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
-then: At Q8, type 3 spaces and nothing else, then submit.</t>
-        </is>
-      </c>
-      <c r="O48" s="6" t="inlineStr">
-        <is>
-          <t>VALID_TYPICAL for every answer</t>
-        </is>
-      </c>
-      <c r="P48" s="6" t="inlineStr">
-        <is>
-          <t>Every answer before Q8 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q8 is the one the claim turns on.</t>
-        </is>
-      </c>
-      <c r="Q48" s="6" t="inlineStr">
-        <is>
-          <t>At Q8, type 3 spaces and nothing else, then submit.</t>
-        </is>
-      </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
-        </is>
-      </c>
-      <c r="S48" s="6" t="inlineStr">
-        <is>
-          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
-        </is>
-      </c>
-      <c r="T48" s="6" t="inlineStr">
-        <is>
-          <t>Q6</t>
-        </is>
-      </c>
-      <c r="U48" s="6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="V48" s="6" t="inlineStr">
-        <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
-        </is>
-      </c>
-      <c r="W48" s="6" t="inlineStr">
-        <is>
-          <t>1. the survey ACCEPTS the answer and moves on</t>
-        </is>
-      </c>
-      <c r="X48" s="6" t="inlineStr">
-        <is>
-          <t>COMPLETE</t>
-        </is>
-      </c>
-      <c r="Y48" s="6" t="inlineStr">
-        <is>
-          <t>Page render per question, plus the ordered sequence log and any validation message shown.</t>
-        </is>
-      </c>
-      <c r="Z48" s="6" t="inlineStr">
-        <is>
-          <t>Q8 | What is the single most important improvement you would suggest? | text | — | Validate: {"max_length": 500}
-Optional</t>
-        </is>
-      </c>
-      <c r="AA48" s="6" t="inlineStr">
-        <is>
-          <t>QRE explicit - stated directly in the questionnaire.</t>
-        </is>
-      </c>
-      <c r="AB48" s="10" t="inlineStr">
-        <is>
-          <t>PROVISIONAL</t>
-        </is>
-      </c>
-      <c r="AC48" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="AD48" s="6" t="inlineStr">
-        <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
-        </is>
-      </c>
-      <c r="AE48" s="6" t="inlineStr">
-        <is>
-          <t>Leans on an unconfirmed reading: whitespace_is_an_answer</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="B49" s="9" t="inlineStr">
-        <is>
-          <t>whole survey</t>
-        </is>
-      </c>
-      <c r="C49" s="7" t="inlineStr">
-        <is>
-          <t>TC-RT03</t>
-        </is>
-      </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>ROUTE</t>
-        </is>
-      </c>
-      <c r="E49" s="6" t="inlineStr">
-        <is>
-          <t>6. Termination / Disposition</t>
-        </is>
-      </c>
-      <c r="F49" s="6" t="inlineStr">
-        <is>
-          <t>1. Flow / Routing</t>
-        </is>
-      </c>
-      <c r="G49" s="7" t="inlineStr">
-        <is>
-          <t>P03</t>
-        </is>
-      </c>
-      <c r="H49" s="6" t="inlineStr">
-        <is>
-          <t>End-to-end journey: COMPLETE by way of routing</t>
-        </is>
-      </c>
-      <c r="I49" s="6" t="inlineStr">
-        <is>
-          <t>Prove that a respondent answering as listed is shown exactly this sequence of questions, in this order, and ends at COMPLETE by way of the routing, checked at ?. Condition: . They should then see: “Thank you. Your response has been recorded.”</t>
-        </is>
-      </c>
-      <c r="J49" s="6" t="inlineStr">
-        <is>
-          <t>Screening someone out incorrectly loses a valid respondent and the money spent recruiting them. Failing to screen someone out puts the wrong person in the sample.</t>
-        </is>
-      </c>
-      <c r="K49" s="6" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="L49" s="6" t="inlineStr">
-        <is>
-          <t>Travel path P03 (Completing respondent — Q5=Yes) as far as the end.</t>
-        </is>
-      </c>
-      <c r="M49" s="6" t="inlineStr">
-        <is>
-          <t>FRESH_RESPONDENT</t>
-        </is>
-      </c>
-      <c r="N49" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; Q1 = In person; Q2 = Very poor; Q3 = Very poor; Q4 = Content relevance; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
 then: Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="O49" s="6" t="inlineStr">
+      <c r="O44" s="6" t="inlineStr">
         <is>
           <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
-      <c r="P49" s="6" t="inlineStr">
+      <c r="P44" s="6" t="inlineStr">
         <is>
           <t>Chosen to walk the whole survey without triggering a screen-out.</t>
         </is>
       </c>
-      <c r="Q49" s="6" t="inlineStr">
+      <c r="Q44" s="6" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="R49" s="6" t="inlineStr">
+      <c r="R44" s="6" t="inlineStr">
         <is>
           <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
         </is>
       </c>
-      <c r="S49" s="6" t="inlineStr">
+      <c r="S44" s="6" t="inlineStr">
         <is>
           <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
         </is>
       </c>
-      <c r="T49" s="6" t="inlineStr">
+      <c r="T44" s="6" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="U49" s="6" t="inlineStr">
+      <c r="U44" s="6" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="V49" s="6" t="inlineStr">
+      <c r="V44" s="6" t="inlineStr">
         <is>
           <t>Each listed question is followed immediately by the next in the sequence.</t>
         </is>
       </c>
-      <c r="W49" s="6" t="inlineStr">
+      <c r="W44" s="6" t="inlineStr">
         <is>
           <t>1. the respondent reaches the normal thank-you page</t>
         </is>
       </c>
-      <c r="X49" s="6" t="inlineStr">
+      <c r="X44" s="6" t="inlineStr">
         <is>
           <t>COMPLETE</t>
         </is>
       </c>
-      <c r="Y49" s="6" t="inlineStr">
+      <c r="Y44" s="6" t="inlineStr">
         <is>
           <t>Page render per question, plus the ordered sequence log and any validation message shown.</t>
         </is>
       </c>
-      <c r="Z49" s="6" t="inlineStr">
+      <c r="Z44" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AA49" s="6" t="inlineStr">
+      <c r="AA44" s="6" t="inlineStr">
         <is>
           <t>QRE explicit - stated directly in the questionnaire.</t>
         </is>
       </c>
-      <c r="AB49" s="8" t="inlineStr">
+      <c r="AB44" s="8" t="inlineStr">
         <is>
           <t>RESOLVED</t>
         </is>
       </c>
-      <c r="AC49" s="8" t="inlineStr">
+      <c r="AC44" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AD49" s="6" t="inlineStr">
+      <c r="AD44" s="6" t="inlineStr">
         <is>
           <t>It does not prove any validation rule: every answer on this path is deliberately valid. It does not prove randomization or quota behaviour.</t>
         </is>
       </c>
-      <c r="AE49" s="6" t="inlineStr">
+      <c r="AE44" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
